--- a/linear_schedule.xlsx
+++ b/linear_schedule.xlsx
@@ -76,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -89,6 +89,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -455,82 +458,142 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="6" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="9" customWidth="1" min="21" max="21"/>
+    <col width="9" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Этап работ</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Начало</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Окончание</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Длит., нед</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Н1</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Н2</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Н3</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Н4</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Н5</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Н6</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Н7</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Н8</t>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Кол-во сотрудников</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Март W1</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Март W2</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Март W3</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Март W4</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Март W5</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>Апрель W1</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>Апрель W2</t>
+        </is>
+      </c>
+      <c r="M1" s="5" t="inlineStr">
+        <is>
+          <t>Апрель W3</t>
+        </is>
+      </c>
+      <c r="N1" s="5" t="inlineStr">
+        <is>
+          <t>Апрель W4</t>
+        </is>
+      </c>
+      <c r="O1" s="5" t="inlineStr">
+        <is>
+          <t>Май W1</t>
+        </is>
+      </c>
+      <c r="P1" s="5" t="inlineStr">
+        <is>
+          <t>Май W2</t>
+        </is>
+      </c>
+      <c r="Q1" s="5" t="inlineStr">
+        <is>
+          <t>Май W3</t>
+        </is>
+      </c>
+      <c r="R1" s="5" t="inlineStr">
+        <is>
+          <t>Май W4</t>
+        </is>
+      </c>
+      <c r="S1" s="5" t="inlineStr">
+        <is>
+          <t>Июнь W1</t>
+        </is>
+      </c>
+      <c r="T1" s="5" t="inlineStr">
+        <is>
+          <t>Июнь W2</t>
+        </is>
+      </c>
+      <c r="U1" s="5" t="inlineStr">
+        <is>
+          <t>Июнь W3</t>
+        </is>
+      </c>
+      <c r="V1" s="5" t="inlineStr">
+        <is>
+          <t>Июнь W4</t>
         </is>
       </c>
     </row>
@@ -542,109 +605,149 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>01.05.2026</t>
+          <t>01.03.2026</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>14.05.2026</t>
+          <t>14.03.2026</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>██</t>
-        </is>
+      <c r="E2" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
           <t>██</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr"/>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>██</t>
+        </is>
+      </c>
       <c r="H2" s="3" t="inlineStr"/>
       <c r="I2" s="3" t="inlineStr"/>
       <c r="J2" s="3" t="inlineStr"/>
       <c r="K2" s="3" t="inlineStr"/>
       <c r="L2" s="3" t="inlineStr"/>
+      <c r="M2" s="3" t="inlineStr"/>
+      <c r="N2" s="3" t="inlineStr"/>
+      <c r="O2" s="3" t="inlineStr"/>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" s="3" t="inlineStr"/>
+      <c r="R2" s="3" t="inlineStr"/>
+      <c r="S2" s="3" t="inlineStr"/>
+      <c r="T2" s="3" t="inlineStr"/>
+      <c r="U2" s="3" t="inlineStr"/>
+      <c r="V2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Земляные работы</t>
+          <t>Земляные работы и основание</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>15.05.2026</t>
+          <t>15.03.2026</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>28.05.2026</t>
+          <t>04.04.2026</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>██</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>██</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>██</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>██</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>██</t>
+        </is>
+      </c>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr"/>
+      <c r="V3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Фундамент</t>
+          <t>Устройство фундамента</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>29.05.2026</t>
+          <t>05.04.2026</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>18.06.2026</t>
+          <t>25.04.2026</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>██</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>██</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>██</t>
-        </is>
-      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="3" t="inlineStr"/>
-      <c r="L4" s="3" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>██</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>██</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>██</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr"/>
+      <c r="O4" s="3" t="inlineStr"/>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr"/>
+      <c r="V4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -654,37 +757,53 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>19.06.2026</t>
+          <t>26.04.2026</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>23.05.2026</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" s="3" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>██</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>██</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>██</t>
-        </is>
-      </c>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>██</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>██</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>██</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>██</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr"/>
+      <c r="V5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -694,65 +813,93 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>24.05.2026</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>13.06.2026</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" s="3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr"/>
       <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>██</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>██</t>
-        </is>
-      </c>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr"/>
       <c r="L6" s="3" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="inlineStr"/>
+      <c r="O6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr">
+        <is>
+          <t>██</t>
+        </is>
+      </c>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>██</t>
+        </is>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>██</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr"/>
+      <c r="V6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Внутренние инженерные сети</t>
+          <t>Инженерные сети</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>14.06.2026</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>27.06.2026</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" s="3" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>██</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>██</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
         <is>
           <t>██</t>
         </is>
@@ -761,34 +908,46 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Отделочные работы</t>
+          <t>Отделочные работы и сдача</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>21.06.2026</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>30.06.2026</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" s="3" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>██</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr"/>
+      <c r="N8" s="3" t="inlineStr"/>
+      <c r="O8" s="3" t="inlineStr"/>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr"/>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="4" t="inlineStr">
+        <is>
+          <t>██</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
         <is>
           <t>██</t>
         </is>

--- a/linear_schedule.xlsx
+++ b/linear_schedule.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,8 +29,13 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -47,6 +52,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="004CAF50"/>
         <bgColor rgb="004CAF50"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E75B6"/>
+        <bgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -76,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -92,6 +109,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -458,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:DW9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -466,490 +492,2912 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="9" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="9" customWidth="1" min="19" max="19"/>
-    <col width="9" customWidth="1" min="20" max="20"/>
-    <col width="9" customWidth="1" min="21" max="21"/>
-    <col width="9" customWidth="1" min="22" max="22"/>
+    <col width="4.2" customWidth="1" min="6" max="6"/>
+    <col width="4.2" customWidth="1" min="7" max="7"/>
+    <col width="4.2" customWidth="1" min="8" max="8"/>
+    <col width="4.2" customWidth="1" min="9" max="9"/>
+    <col width="4.2" customWidth="1" min="10" max="10"/>
+    <col width="4.2" customWidth="1" min="11" max="11"/>
+    <col width="4.2" customWidth="1" min="12" max="12"/>
+    <col width="4.2" customWidth="1" min="13" max="13"/>
+    <col width="4.2" customWidth="1" min="14" max="14"/>
+    <col width="4.2" customWidth="1" min="15" max="15"/>
+    <col width="4.2" customWidth="1" min="16" max="16"/>
+    <col width="4.2" customWidth="1" min="17" max="17"/>
+    <col width="4.2" customWidth="1" min="18" max="18"/>
+    <col width="4.2" customWidth="1" min="19" max="19"/>
+    <col width="4.2" customWidth="1" min="20" max="20"/>
+    <col width="4.2" customWidth="1" min="21" max="21"/>
+    <col width="4.2" customWidth="1" min="22" max="22"/>
+    <col width="4.2" customWidth="1" min="23" max="23"/>
+    <col width="4.2" customWidth="1" min="24" max="24"/>
+    <col width="4.2" customWidth="1" min="25" max="25"/>
+    <col width="4.2" customWidth="1" min="26" max="26"/>
+    <col width="4.2" customWidth="1" min="27" max="27"/>
+    <col width="4.2" customWidth="1" min="28" max="28"/>
+    <col width="4.2" customWidth="1" min="29" max="29"/>
+    <col width="4.2" customWidth="1" min="30" max="30"/>
+    <col width="4.2" customWidth="1" min="31" max="31"/>
+    <col width="4.2" customWidth="1" min="32" max="32"/>
+    <col width="4.2" customWidth="1" min="33" max="33"/>
+    <col width="4.2" customWidth="1" min="34" max="34"/>
+    <col width="4.2" customWidth="1" min="35" max="35"/>
+    <col width="4.2" customWidth="1" min="36" max="36"/>
+    <col width="4.2" customWidth="1" min="37" max="37"/>
+    <col width="4.2" customWidth="1" min="38" max="38"/>
+    <col width="4.2" customWidth="1" min="39" max="39"/>
+    <col width="4.2" customWidth="1" min="40" max="40"/>
+    <col width="4.2" customWidth="1" min="41" max="41"/>
+    <col width="4.2" customWidth="1" min="42" max="42"/>
+    <col width="4.2" customWidth="1" min="43" max="43"/>
+    <col width="4.2" customWidth="1" min="44" max="44"/>
+    <col width="4.2" customWidth="1" min="45" max="45"/>
+    <col width="4.2" customWidth="1" min="46" max="46"/>
+    <col width="4.2" customWidth="1" min="47" max="47"/>
+    <col width="4.2" customWidth="1" min="48" max="48"/>
+    <col width="4.2" customWidth="1" min="49" max="49"/>
+    <col width="4.2" customWidth="1" min="50" max="50"/>
+    <col width="4.2" customWidth="1" min="51" max="51"/>
+    <col width="4.2" customWidth="1" min="52" max="52"/>
+    <col width="4.2" customWidth="1" min="53" max="53"/>
+    <col width="4.2" customWidth="1" min="54" max="54"/>
+    <col width="4.2" customWidth="1" min="55" max="55"/>
+    <col width="4.2" customWidth="1" min="56" max="56"/>
+    <col width="4.2" customWidth="1" min="57" max="57"/>
+    <col width="4.2" customWidth="1" min="58" max="58"/>
+    <col width="4.2" customWidth="1" min="59" max="59"/>
+    <col width="4.2" customWidth="1" min="60" max="60"/>
+    <col width="4.2" customWidth="1" min="61" max="61"/>
+    <col width="4.2" customWidth="1" min="62" max="62"/>
+    <col width="4.2" customWidth="1" min="63" max="63"/>
+    <col width="4.2" customWidth="1" min="64" max="64"/>
+    <col width="4.2" customWidth="1" min="65" max="65"/>
+    <col width="4.2" customWidth="1" min="66" max="66"/>
+    <col width="4.2" customWidth="1" min="67" max="67"/>
+    <col width="4.2" customWidth="1" min="68" max="68"/>
+    <col width="4.2" customWidth="1" min="69" max="69"/>
+    <col width="4.2" customWidth="1" min="70" max="70"/>
+    <col width="4.2" customWidth="1" min="71" max="71"/>
+    <col width="4.2" customWidth="1" min="72" max="72"/>
+    <col width="4.2" customWidth="1" min="73" max="73"/>
+    <col width="4.2" customWidth="1" min="74" max="74"/>
+    <col width="4.2" customWidth="1" min="75" max="75"/>
+    <col width="4.2" customWidth="1" min="76" max="76"/>
+    <col width="4.2" customWidth="1" min="77" max="77"/>
+    <col width="4.2" customWidth="1" min="78" max="78"/>
+    <col width="4.2" customWidth="1" min="79" max="79"/>
+    <col width="4.2" customWidth="1" min="80" max="80"/>
+    <col width="4.2" customWidth="1" min="81" max="81"/>
+    <col width="4.2" customWidth="1" min="82" max="82"/>
+    <col width="4.2" customWidth="1" min="83" max="83"/>
+    <col width="4.2" customWidth="1" min="84" max="84"/>
+    <col width="4.2" customWidth="1" min="85" max="85"/>
+    <col width="4.2" customWidth="1" min="86" max="86"/>
+    <col width="4.2" customWidth="1" min="87" max="87"/>
+    <col width="4.2" customWidth="1" min="88" max="88"/>
+    <col width="4.2" customWidth="1" min="89" max="89"/>
+    <col width="4.2" customWidth="1" min="90" max="90"/>
+    <col width="4.2" customWidth="1" min="91" max="91"/>
+    <col width="4.2" customWidth="1" min="92" max="92"/>
+    <col width="4.2" customWidth="1" min="93" max="93"/>
+    <col width="4.2" customWidth="1" min="94" max="94"/>
+    <col width="4.2" customWidth="1" min="95" max="95"/>
+    <col width="4.2" customWidth="1" min="96" max="96"/>
+    <col width="4.2" customWidth="1" min="97" max="97"/>
+    <col width="4.2" customWidth="1" min="98" max="98"/>
+    <col width="4.2" customWidth="1" min="99" max="99"/>
+    <col width="4.2" customWidth="1" min="100" max="100"/>
+    <col width="4.2" customWidth="1" min="101" max="101"/>
+    <col width="4.2" customWidth="1" min="102" max="102"/>
+    <col width="4.2" customWidth="1" min="103" max="103"/>
+    <col width="4.2" customWidth="1" min="104" max="104"/>
+    <col width="4.2" customWidth="1" min="105" max="105"/>
+    <col width="4.2" customWidth="1" min="106" max="106"/>
+    <col width="4.2" customWidth="1" min="107" max="107"/>
+    <col width="4.2" customWidth="1" min="108" max="108"/>
+    <col width="4.2" customWidth="1" min="109" max="109"/>
+    <col width="4.2" customWidth="1" min="110" max="110"/>
+    <col width="4.2" customWidth="1" min="111" max="111"/>
+    <col width="4.2" customWidth="1" min="112" max="112"/>
+    <col width="4.2" customWidth="1" min="113" max="113"/>
+    <col width="4.2" customWidth="1" min="114" max="114"/>
+    <col width="4.2" customWidth="1" min="115" max="115"/>
+    <col width="4.2" customWidth="1" min="116" max="116"/>
+    <col width="4.2" customWidth="1" min="117" max="117"/>
+    <col width="4.2" customWidth="1" min="118" max="118"/>
+    <col width="4.2" customWidth="1" min="119" max="119"/>
+    <col width="4.2" customWidth="1" min="120" max="120"/>
+    <col width="4.2" customWidth="1" min="121" max="121"/>
+    <col width="4.2" customWidth="1" min="122" max="122"/>
+    <col width="4.2" customWidth="1" min="123" max="123"/>
+    <col width="4.2" customWidth="1" min="124" max="124"/>
+    <col width="4.2" customWidth="1" min="125" max="125"/>
+    <col width="4.2" customWidth="1" min="126" max="126"/>
+    <col width="4.2" customWidth="1" min="127" max="127"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Этап работ</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Начало</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Окончание</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>Длит., нед</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Длит., дн</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Кол-во сотрудников</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
-        <is>
-          <t>Март W1</t>
-        </is>
-      </c>
-      <c r="G1" s="5" t="inlineStr">
-        <is>
-          <t>Март W2</t>
-        </is>
-      </c>
-      <c r="H1" s="5" t="inlineStr">
-        <is>
-          <t>Март W3</t>
-        </is>
-      </c>
-      <c r="I1" s="5" t="inlineStr">
-        <is>
-          <t>Март W4</t>
-        </is>
-      </c>
-      <c r="J1" s="5" t="inlineStr">
-        <is>
-          <t>Март W5</t>
-        </is>
-      </c>
-      <c r="K1" s="5" t="inlineStr">
-        <is>
-          <t>Апрель W1</t>
-        </is>
-      </c>
-      <c r="L1" s="5" t="inlineStr">
-        <is>
-          <t>Апрель W2</t>
-        </is>
-      </c>
-      <c r="M1" s="5" t="inlineStr">
-        <is>
-          <t>Апрель W3</t>
-        </is>
-      </c>
-      <c r="N1" s="5" t="inlineStr">
-        <is>
-          <t>Апрель W4</t>
-        </is>
-      </c>
-      <c r="O1" s="5" t="inlineStr">
-        <is>
-          <t>Май W1</t>
-        </is>
-      </c>
-      <c r="P1" s="5" t="inlineStr">
-        <is>
-          <t>Май W2</t>
-        </is>
-      </c>
-      <c r="Q1" s="5" t="inlineStr">
-        <is>
-          <t>Май W3</t>
-        </is>
-      </c>
-      <c r="R1" s="5" t="inlineStr">
-        <is>
-          <t>Май W4</t>
-        </is>
-      </c>
-      <c r="S1" s="5" t="inlineStr">
-        <is>
-          <t>Июнь W1</t>
-        </is>
-      </c>
-      <c r="T1" s="5" t="inlineStr">
-        <is>
-          <t>Июнь W2</t>
-        </is>
-      </c>
-      <c r="U1" s="5" t="inlineStr">
-        <is>
-          <t>Июнь W3</t>
-        </is>
-      </c>
-      <c r="V1" s="5" t="inlineStr">
-        <is>
-          <t>Июнь W4</t>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>01.03</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>02.03</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>03.03</t>
+        </is>
+      </c>
+      <c r="I1" s="6" t="inlineStr">
+        <is>
+          <t>04.03</t>
+        </is>
+      </c>
+      <c r="J1" s="6" t="inlineStr">
+        <is>
+          <t>05.03</t>
+        </is>
+      </c>
+      <c r="K1" s="6" t="inlineStr">
+        <is>
+          <t>06.03</t>
+        </is>
+      </c>
+      <c r="L1" s="6" t="inlineStr">
+        <is>
+          <t>07.03</t>
+        </is>
+      </c>
+      <c r="M1" s="6" t="inlineStr">
+        <is>
+          <t>08.03</t>
+        </is>
+      </c>
+      <c r="N1" s="6" t="inlineStr">
+        <is>
+          <t>09.03</t>
+        </is>
+      </c>
+      <c r="O1" s="6" t="inlineStr">
+        <is>
+          <t>10.03</t>
+        </is>
+      </c>
+      <c r="P1" s="6" t="inlineStr">
+        <is>
+          <t>11.03</t>
+        </is>
+      </c>
+      <c r="Q1" s="6" t="inlineStr">
+        <is>
+          <t>12.03</t>
+        </is>
+      </c>
+      <c r="R1" s="6" t="inlineStr">
+        <is>
+          <t>13.03</t>
+        </is>
+      </c>
+      <c r="S1" s="6" t="inlineStr">
+        <is>
+          <t>14.03</t>
+        </is>
+      </c>
+      <c r="T1" s="6" t="inlineStr">
+        <is>
+          <t>15.03</t>
+        </is>
+      </c>
+      <c r="U1" s="6" t="inlineStr">
+        <is>
+          <t>16.03</t>
+        </is>
+      </c>
+      <c r="V1" s="6" t="inlineStr">
+        <is>
+          <t>17.03</t>
+        </is>
+      </c>
+      <c r="W1" s="6" t="inlineStr">
+        <is>
+          <t>18.03</t>
+        </is>
+      </c>
+      <c r="X1" s="6" t="inlineStr">
+        <is>
+          <t>19.03</t>
+        </is>
+      </c>
+      <c r="Y1" s="6" t="inlineStr">
+        <is>
+          <t>20.03</t>
+        </is>
+      </c>
+      <c r="Z1" s="6" t="inlineStr">
+        <is>
+          <t>21.03</t>
+        </is>
+      </c>
+      <c r="AA1" s="6" t="inlineStr">
+        <is>
+          <t>22.03</t>
+        </is>
+      </c>
+      <c r="AB1" s="6" t="inlineStr">
+        <is>
+          <t>23.03</t>
+        </is>
+      </c>
+      <c r="AC1" s="6" t="inlineStr">
+        <is>
+          <t>24.03</t>
+        </is>
+      </c>
+      <c r="AD1" s="6" t="inlineStr">
+        <is>
+          <t>25.03</t>
+        </is>
+      </c>
+      <c r="AE1" s="6" t="inlineStr">
+        <is>
+          <t>26.03</t>
+        </is>
+      </c>
+      <c r="AF1" s="6" t="inlineStr">
+        <is>
+          <t>27.03</t>
+        </is>
+      </c>
+      <c r="AG1" s="6" t="inlineStr">
+        <is>
+          <t>28.03</t>
+        </is>
+      </c>
+      <c r="AH1" s="6" t="inlineStr">
+        <is>
+          <t>29.03</t>
+        </is>
+      </c>
+      <c r="AI1" s="6" t="inlineStr">
+        <is>
+          <t>30.03</t>
+        </is>
+      </c>
+      <c r="AJ1" s="6" t="inlineStr">
+        <is>
+          <t>31.03</t>
+        </is>
+      </c>
+      <c r="AK1" s="6" t="inlineStr">
+        <is>
+          <t>01.04</t>
+        </is>
+      </c>
+      <c r="AL1" s="6" t="inlineStr">
+        <is>
+          <t>02.04</t>
+        </is>
+      </c>
+      <c r="AM1" s="6" t="inlineStr">
+        <is>
+          <t>03.04</t>
+        </is>
+      </c>
+      <c r="AN1" s="6" t="inlineStr">
+        <is>
+          <t>04.04</t>
+        </is>
+      </c>
+      <c r="AO1" s="6" t="inlineStr">
+        <is>
+          <t>05.04</t>
+        </is>
+      </c>
+      <c r="AP1" s="6" t="inlineStr">
+        <is>
+          <t>06.04</t>
+        </is>
+      </c>
+      <c r="AQ1" s="6" t="inlineStr">
+        <is>
+          <t>07.04</t>
+        </is>
+      </c>
+      <c r="AR1" s="6" t="inlineStr">
+        <is>
+          <t>08.04</t>
+        </is>
+      </c>
+      <c r="AS1" s="6" t="inlineStr">
+        <is>
+          <t>09.04</t>
+        </is>
+      </c>
+      <c r="AT1" s="6" t="inlineStr">
+        <is>
+          <t>10.04</t>
+        </is>
+      </c>
+      <c r="AU1" s="6" t="inlineStr">
+        <is>
+          <t>11.04</t>
+        </is>
+      </c>
+      <c r="AV1" s="6" t="inlineStr">
+        <is>
+          <t>12.04</t>
+        </is>
+      </c>
+      <c r="AW1" s="6" t="inlineStr">
+        <is>
+          <t>13.04</t>
+        </is>
+      </c>
+      <c r="AX1" s="6" t="inlineStr">
+        <is>
+          <t>14.04</t>
+        </is>
+      </c>
+      <c r="AY1" s="6" t="inlineStr">
+        <is>
+          <t>15.04</t>
+        </is>
+      </c>
+      <c r="AZ1" s="6" t="inlineStr">
+        <is>
+          <t>16.04</t>
+        </is>
+      </c>
+      <c r="BA1" s="6" t="inlineStr">
+        <is>
+          <t>17.04</t>
+        </is>
+      </c>
+      <c r="BB1" s="6" t="inlineStr">
+        <is>
+          <t>18.04</t>
+        </is>
+      </c>
+      <c r="BC1" s="6" t="inlineStr">
+        <is>
+          <t>19.04</t>
+        </is>
+      </c>
+      <c r="BD1" s="6" t="inlineStr">
+        <is>
+          <t>20.04</t>
+        </is>
+      </c>
+      <c r="BE1" s="6" t="inlineStr">
+        <is>
+          <t>21.04</t>
+        </is>
+      </c>
+      <c r="BF1" s="6" t="inlineStr">
+        <is>
+          <t>22.04</t>
+        </is>
+      </c>
+      <c r="BG1" s="6" t="inlineStr">
+        <is>
+          <t>23.04</t>
+        </is>
+      </c>
+      <c r="BH1" s="6" t="inlineStr">
+        <is>
+          <t>24.04</t>
+        </is>
+      </c>
+      <c r="BI1" s="6" t="inlineStr">
+        <is>
+          <t>25.04</t>
+        </is>
+      </c>
+      <c r="BJ1" s="6" t="inlineStr">
+        <is>
+          <t>26.04</t>
+        </is>
+      </c>
+      <c r="BK1" s="6" t="inlineStr">
+        <is>
+          <t>27.04</t>
+        </is>
+      </c>
+      <c r="BL1" s="6" t="inlineStr">
+        <is>
+          <t>28.04</t>
+        </is>
+      </c>
+      <c r="BM1" s="6" t="inlineStr">
+        <is>
+          <t>29.04</t>
+        </is>
+      </c>
+      <c r="BN1" s="6" t="inlineStr">
+        <is>
+          <t>30.04</t>
+        </is>
+      </c>
+      <c r="BO1" s="6" t="inlineStr">
+        <is>
+          <t>01.05</t>
+        </is>
+      </c>
+      <c r="BP1" s="6" t="inlineStr">
+        <is>
+          <t>02.05</t>
+        </is>
+      </c>
+      <c r="BQ1" s="6" t="inlineStr">
+        <is>
+          <t>03.05</t>
+        </is>
+      </c>
+      <c r="BR1" s="6" t="inlineStr">
+        <is>
+          <t>04.05</t>
+        </is>
+      </c>
+      <c r="BS1" s="6" t="inlineStr">
+        <is>
+          <t>05.05</t>
+        </is>
+      </c>
+      <c r="BT1" s="6" t="inlineStr">
+        <is>
+          <t>06.05</t>
+        </is>
+      </c>
+      <c r="BU1" s="6" t="inlineStr">
+        <is>
+          <t>07.05</t>
+        </is>
+      </c>
+      <c r="BV1" s="6" t="inlineStr">
+        <is>
+          <t>08.05</t>
+        </is>
+      </c>
+      <c r="BW1" s="6" t="inlineStr">
+        <is>
+          <t>09.05</t>
+        </is>
+      </c>
+      <c r="BX1" s="6" t="inlineStr">
+        <is>
+          <t>10.05</t>
+        </is>
+      </c>
+      <c r="BY1" s="6" t="inlineStr">
+        <is>
+          <t>11.05</t>
+        </is>
+      </c>
+      <c r="BZ1" s="6" t="inlineStr">
+        <is>
+          <t>12.05</t>
+        </is>
+      </c>
+      <c r="CA1" s="6" t="inlineStr">
+        <is>
+          <t>13.05</t>
+        </is>
+      </c>
+      <c r="CB1" s="6" t="inlineStr">
+        <is>
+          <t>14.05</t>
+        </is>
+      </c>
+      <c r="CC1" s="6" t="inlineStr">
+        <is>
+          <t>15.05</t>
+        </is>
+      </c>
+      <c r="CD1" s="6" t="inlineStr">
+        <is>
+          <t>16.05</t>
+        </is>
+      </c>
+      <c r="CE1" s="6" t="inlineStr">
+        <is>
+          <t>17.05</t>
+        </is>
+      </c>
+      <c r="CF1" s="6" t="inlineStr">
+        <is>
+          <t>18.05</t>
+        </is>
+      </c>
+      <c r="CG1" s="6" t="inlineStr">
+        <is>
+          <t>19.05</t>
+        </is>
+      </c>
+      <c r="CH1" s="6" t="inlineStr">
+        <is>
+          <t>20.05</t>
+        </is>
+      </c>
+      <c r="CI1" s="6" t="inlineStr">
+        <is>
+          <t>21.05</t>
+        </is>
+      </c>
+      <c r="CJ1" s="6" t="inlineStr">
+        <is>
+          <t>22.05</t>
+        </is>
+      </c>
+      <c r="CK1" s="6" t="inlineStr">
+        <is>
+          <t>23.05</t>
+        </is>
+      </c>
+      <c r="CL1" s="6" t="inlineStr">
+        <is>
+          <t>24.05</t>
+        </is>
+      </c>
+      <c r="CM1" s="6" t="inlineStr">
+        <is>
+          <t>25.05</t>
+        </is>
+      </c>
+      <c r="CN1" s="6" t="inlineStr">
+        <is>
+          <t>26.05</t>
+        </is>
+      </c>
+      <c r="CO1" s="6" t="inlineStr">
+        <is>
+          <t>27.05</t>
+        </is>
+      </c>
+      <c r="CP1" s="6" t="inlineStr">
+        <is>
+          <t>28.05</t>
+        </is>
+      </c>
+      <c r="CQ1" s="6" t="inlineStr">
+        <is>
+          <t>29.05</t>
+        </is>
+      </c>
+      <c r="CR1" s="6" t="inlineStr">
+        <is>
+          <t>30.05</t>
+        </is>
+      </c>
+      <c r="CS1" s="6" t="inlineStr">
+        <is>
+          <t>31.05</t>
+        </is>
+      </c>
+      <c r="CT1" s="6" t="inlineStr">
+        <is>
+          <t>01.06</t>
+        </is>
+      </c>
+      <c r="CU1" s="6" t="inlineStr">
+        <is>
+          <t>02.06</t>
+        </is>
+      </c>
+      <c r="CV1" s="6" t="inlineStr">
+        <is>
+          <t>03.06</t>
+        </is>
+      </c>
+      <c r="CW1" s="6" t="inlineStr">
+        <is>
+          <t>04.06</t>
+        </is>
+      </c>
+      <c r="CX1" s="6" t="inlineStr">
+        <is>
+          <t>05.06</t>
+        </is>
+      </c>
+      <c r="CY1" s="6" t="inlineStr">
+        <is>
+          <t>06.06</t>
+        </is>
+      </c>
+      <c r="CZ1" s="6" t="inlineStr">
+        <is>
+          <t>07.06</t>
+        </is>
+      </c>
+      <c r="DA1" s="6" t="inlineStr">
+        <is>
+          <t>08.06</t>
+        </is>
+      </c>
+      <c r="DB1" s="6" t="inlineStr">
+        <is>
+          <t>09.06</t>
+        </is>
+      </c>
+      <c r="DC1" s="6" t="inlineStr">
+        <is>
+          <t>10.06</t>
+        </is>
+      </c>
+      <c r="DD1" s="6" t="inlineStr">
+        <is>
+          <t>11.06</t>
+        </is>
+      </c>
+      <c r="DE1" s="6" t="inlineStr">
+        <is>
+          <t>12.06</t>
+        </is>
+      </c>
+      <c r="DF1" s="6" t="inlineStr">
+        <is>
+          <t>13.06</t>
+        </is>
+      </c>
+      <c r="DG1" s="6" t="inlineStr">
+        <is>
+          <t>14.06</t>
+        </is>
+      </c>
+      <c r="DH1" s="6" t="inlineStr">
+        <is>
+          <t>15.06</t>
+        </is>
+      </c>
+      <c r="DI1" s="6" t="inlineStr">
+        <is>
+          <t>16.06</t>
+        </is>
+      </c>
+      <c r="DJ1" s="6" t="inlineStr">
+        <is>
+          <t>17.06</t>
+        </is>
+      </c>
+      <c r="DK1" s="6" t="inlineStr">
+        <is>
+          <t>18.06</t>
+        </is>
+      </c>
+      <c r="DL1" s="6" t="inlineStr">
+        <is>
+          <t>19.06</t>
+        </is>
+      </c>
+      <c r="DM1" s="6" t="inlineStr">
+        <is>
+          <t>20.06</t>
+        </is>
+      </c>
+      <c r="DN1" s="6" t="inlineStr">
+        <is>
+          <t>21.06</t>
+        </is>
+      </c>
+      <c r="DO1" s="6" t="inlineStr">
+        <is>
+          <t>22.06</t>
+        </is>
+      </c>
+      <c r="DP1" s="6" t="inlineStr">
+        <is>
+          <t>23.06</t>
+        </is>
+      </c>
+      <c r="DQ1" s="6" t="inlineStr">
+        <is>
+          <t>24.06</t>
+        </is>
+      </c>
+      <c r="DR1" s="6" t="inlineStr">
+        <is>
+          <t>25.06</t>
+        </is>
+      </c>
+      <c r="DS1" s="6" t="inlineStr">
+        <is>
+          <t>26.06</t>
+        </is>
+      </c>
+      <c r="DT1" s="6" t="inlineStr">
+        <is>
+          <t>27.06</t>
+        </is>
+      </c>
+      <c r="DU1" s="6" t="inlineStr">
+        <is>
+          <t>28.06</t>
+        </is>
+      </c>
+      <c r="DV1" s="6" t="inlineStr">
+        <is>
+          <t>29.06</t>
+        </is>
+      </c>
+      <c r="DW1" s="6" t="inlineStr">
+        <is>
+          <t>30.06</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Подготовительные работы</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>01.03.2026</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>14.03.2026</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>██</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>██</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
-      <c r="J2" s="3" t="inlineStr"/>
-      <c r="K2" s="3" t="inlineStr"/>
-      <c r="L2" s="3" t="inlineStr"/>
-      <c r="M2" s="3" t="inlineStr"/>
-      <c r="N2" s="3" t="inlineStr"/>
-      <c r="O2" s="3" t="inlineStr"/>
-      <c r="P2" s="3" t="inlineStr"/>
-      <c r="Q2" s="3" t="inlineStr"/>
-      <c r="R2" s="3" t="inlineStr"/>
-      <c r="S2" s="3" t="inlineStr"/>
-      <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr"/>
-      <c r="V2" s="3" t="inlineStr"/>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr"/>
+      <c r="B2" s="7" t="inlineStr"/>
+      <c r="C2" s="7" t="inlineStr"/>
+      <c r="D2" s="7" t="inlineStr"/>
+      <c r="E2" s="7" t="inlineStr"/>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>Вс</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>Пн</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>Вт</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>Ср</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>Чт</t>
+        </is>
+      </c>
+      <c r="K2" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>Сб</t>
+        </is>
+      </c>
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t>Вс</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="inlineStr">
+        <is>
+          <t>Пн</t>
+        </is>
+      </c>
+      <c r="O2" s="7" t="inlineStr">
+        <is>
+          <t>Вт</t>
+        </is>
+      </c>
+      <c r="P2" s="7" t="inlineStr">
+        <is>
+          <t>Ср</t>
+        </is>
+      </c>
+      <c r="Q2" s="7" t="inlineStr">
+        <is>
+          <t>Чт</t>
+        </is>
+      </c>
+      <c r="R2" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>Сб</t>
+        </is>
+      </c>
+      <c r="T2" s="7" t="inlineStr">
+        <is>
+          <t>Вс</t>
+        </is>
+      </c>
+      <c r="U2" s="7" t="inlineStr">
+        <is>
+          <t>Пн</t>
+        </is>
+      </c>
+      <c r="V2" s="7" t="inlineStr">
+        <is>
+          <t>Вт</t>
+        </is>
+      </c>
+      <c r="W2" s="7" t="inlineStr">
+        <is>
+          <t>Ср</t>
+        </is>
+      </c>
+      <c r="X2" s="7" t="inlineStr">
+        <is>
+          <t>Чт</t>
+        </is>
+      </c>
+      <c r="Y2" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="Z2" s="7" t="inlineStr">
+        <is>
+          <t>Сб</t>
+        </is>
+      </c>
+      <c r="AA2" s="7" t="inlineStr">
+        <is>
+          <t>Вс</t>
+        </is>
+      </c>
+      <c r="AB2" s="7" t="inlineStr">
+        <is>
+          <t>Пн</t>
+        </is>
+      </c>
+      <c r="AC2" s="7" t="inlineStr">
+        <is>
+          <t>Вт</t>
+        </is>
+      </c>
+      <c r="AD2" s="7" t="inlineStr">
+        <is>
+          <t>Ср</t>
+        </is>
+      </c>
+      <c r="AE2" s="7" t="inlineStr">
+        <is>
+          <t>Чт</t>
+        </is>
+      </c>
+      <c r="AF2" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="AG2" s="7" t="inlineStr">
+        <is>
+          <t>Сб</t>
+        </is>
+      </c>
+      <c r="AH2" s="7" t="inlineStr">
+        <is>
+          <t>Вс</t>
+        </is>
+      </c>
+      <c r="AI2" s="7" t="inlineStr">
+        <is>
+          <t>Пн</t>
+        </is>
+      </c>
+      <c r="AJ2" s="7" t="inlineStr">
+        <is>
+          <t>Вт</t>
+        </is>
+      </c>
+      <c r="AK2" s="7" t="inlineStr">
+        <is>
+          <t>Ср</t>
+        </is>
+      </c>
+      <c r="AL2" s="7" t="inlineStr">
+        <is>
+          <t>Чт</t>
+        </is>
+      </c>
+      <c r="AM2" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="AN2" s="7" t="inlineStr">
+        <is>
+          <t>Сб</t>
+        </is>
+      </c>
+      <c r="AO2" s="7" t="inlineStr">
+        <is>
+          <t>Вс</t>
+        </is>
+      </c>
+      <c r="AP2" s="7" t="inlineStr">
+        <is>
+          <t>Пн</t>
+        </is>
+      </c>
+      <c r="AQ2" s="7" t="inlineStr">
+        <is>
+          <t>Вт</t>
+        </is>
+      </c>
+      <c r="AR2" s="7" t="inlineStr">
+        <is>
+          <t>Ср</t>
+        </is>
+      </c>
+      <c r="AS2" s="7" t="inlineStr">
+        <is>
+          <t>Чт</t>
+        </is>
+      </c>
+      <c r="AT2" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="AU2" s="7" t="inlineStr">
+        <is>
+          <t>Сб</t>
+        </is>
+      </c>
+      <c r="AV2" s="7" t="inlineStr">
+        <is>
+          <t>Вс</t>
+        </is>
+      </c>
+      <c r="AW2" s="7" t="inlineStr">
+        <is>
+          <t>Пн</t>
+        </is>
+      </c>
+      <c r="AX2" s="7" t="inlineStr">
+        <is>
+          <t>Вт</t>
+        </is>
+      </c>
+      <c r="AY2" s="7" t="inlineStr">
+        <is>
+          <t>Ср</t>
+        </is>
+      </c>
+      <c r="AZ2" s="7" t="inlineStr">
+        <is>
+          <t>Чт</t>
+        </is>
+      </c>
+      <c r="BA2" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="BB2" s="7" t="inlineStr">
+        <is>
+          <t>Сб</t>
+        </is>
+      </c>
+      <c r="BC2" s="7" t="inlineStr">
+        <is>
+          <t>Вс</t>
+        </is>
+      </c>
+      <c r="BD2" s="7" t="inlineStr">
+        <is>
+          <t>Пн</t>
+        </is>
+      </c>
+      <c r="BE2" s="7" t="inlineStr">
+        <is>
+          <t>Вт</t>
+        </is>
+      </c>
+      <c r="BF2" s="7" t="inlineStr">
+        <is>
+          <t>Ср</t>
+        </is>
+      </c>
+      <c r="BG2" s="7" t="inlineStr">
+        <is>
+          <t>Чт</t>
+        </is>
+      </c>
+      <c r="BH2" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="BI2" s="7" t="inlineStr">
+        <is>
+          <t>Сб</t>
+        </is>
+      </c>
+      <c r="BJ2" s="7" t="inlineStr">
+        <is>
+          <t>Вс</t>
+        </is>
+      </c>
+      <c r="BK2" s="7" t="inlineStr">
+        <is>
+          <t>Пн</t>
+        </is>
+      </c>
+      <c r="BL2" s="7" t="inlineStr">
+        <is>
+          <t>Вт</t>
+        </is>
+      </c>
+      <c r="BM2" s="7" t="inlineStr">
+        <is>
+          <t>Ср</t>
+        </is>
+      </c>
+      <c r="BN2" s="7" t="inlineStr">
+        <is>
+          <t>Чт</t>
+        </is>
+      </c>
+      <c r="BO2" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="BP2" s="7" t="inlineStr">
+        <is>
+          <t>Сб</t>
+        </is>
+      </c>
+      <c r="BQ2" s="7" t="inlineStr">
+        <is>
+          <t>Вс</t>
+        </is>
+      </c>
+      <c r="BR2" s="7" t="inlineStr">
+        <is>
+          <t>Пн</t>
+        </is>
+      </c>
+      <c r="BS2" s="7" t="inlineStr">
+        <is>
+          <t>Вт</t>
+        </is>
+      </c>
+      <c r="BT2" s="7" t="inlineStr">
+        <is>
+          <t>Ср</t>
+        </is>
+      </c>
+      <c r="BU2" s="7" t="inlineStr">
+        <is>
+          <t>Чт</t>
+        </is>
+      </c>
+      <c r="BV2" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="BW2" s="7" t="inlineStr">
+        <is>
+          <t>Сб</t>
+        </is>
+      </c>
+      <c r="BX2" s="7" t="inlineStr">
+        <is>
+          <t>Вс</t>
+        </is>
+      </c>
+      <c r="BY2" s="7" t="inlineStr">
+        <is>
+          <t>Пн</t>
+        </is>
+      </c>
+      <c r="BZ2" s="7" t="inlineStr">
+        <is>
+          <t>Вт</t>
+        </is>
+      </c>
+      <c r="CA2" s="7" t="inlineStr">
+        <is>
+          <t>Ср</t>
+        </is>
+      </c>
+      <c r="CB2" s="7" t="inlineStr">
+        <is>
+          <t>Чт</t>
+        </is>
+      </c>
+      <c r="CC2" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="CD2" s="7" t="inlineStr">
+        <is>
+          <t>Сб</t>
+        </is>
+      </c>
+      <c r="CE2" s="7" t="inlineStr">
+        <is>
+          <t>Вс</t>
+        </is>
+      </c>
+      <c r="CF2" s="7" t="inlineStr">
+        <is>
+          <t>Пн</t>
+        </is>
+      </c>
+      <c r="CG2" s="7" t="inlineStr">
+        <is>
+          <t>Вт</t>
+        </is>
+      </c>
+      <c r="CH2" s="7" t="inlineStr">
+        <is>
+          <t>Ср</t>
+        </is>
+      </c>
+      <c r="CI2" s="7" t="inlineStr">
+        <is>
+          <t>Чт</t>
+        </is>
+      </c>
+      <c r="CJ2" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="CK2" s="7" t="inlineStr">
+        <is>
+          <t>Сб</t>
+        </is>
+      </c>
+      <c r="CL2" s="7" t="inlineStr">
+        <is>
+          <t>Вс</t>
+        </is>
+      </c>
+      <c r="CM2" s="7" t="inlineStr">
+        <is>
+          <t>Пн</t>
+        </is>
+      </c>
+      <c r="CN2" s="7" t="inlineStr">
+        <is>
+          <t>Вт</t>
+        </is>
+      </c>
+      <c r="CO2" s="7" t="inlineStr">
+        <is>
+          <t>Ср</t>
+        </is>
+      </c>
+      <c r="CP2" s="7" t="inlineStr">
+        <is>
+          <t>Чт</t>
+        </is>
+      </c>
+      <c r="CQ2" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="CR2" s="7" t="inlineStr">
+        <is>
+          <t>Сб</t>
+        </is>
+      </c>
+      <c r="CS2" s="7" t="inlineStr">
+        <is>
+          <t>Вс</t>
+        </is>
+      </c>
+      <c r="CT2" s="7" t="inlineStr">
+        <is>
+          <t>Пн</t>
+        </is>
+      </c>
+      <c r="CU2" s="7" t="inlineStr">
+        <is>
+          <t>Вт</t>
+        </is>
+      </c>
+      <c r="CV2" s="7" t="inlineStr">
+        <is>
+          <t>Ср</t>
+        </is>
+      </c>
+      <c r="CW2" s="7" t="inlineStr">
+        <is>
+          <t>Чт</t>
+        </is>
+      </c>
+      <c r="CX2" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="CY2" s="7" t="inlineStr">
+        <is>
+          <t>Сб</t>
+        </is>
+      </c>
+      <c r="CZ2" s="7" t="inlineStr">
+        <is>
+          <t>Вс</t>
+        </is>
+      </c>
+      <c r="DA2" s="7" t="inlineStr">
+        <is>
+          <t>Пн</t>
+        </is>
+      </c>
+      <c r="DB2" s="7" t="inlineStr">
+        <is>
+          <t>Вт</t>
+        </is>
+      </c>
+      <c r="DC2" s="7" t="inlineStr">
+        <is>
+          <t>Ср</t>
+        </is>
+      </c>
+      <c r="DD2" s="7" t="inlineStr">
+        <is>
+          <t>Чт</t>
+        </is>
+      </c>
+      <c r="DE2" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="DF2" s="7" t="inlineStr">
+        <is>
+          <t>Сб</t>
+        </is>
+      </c>
+      <c r="DG2" s="7" t="inlineStr">
+        <is>
+          <t>Вс</t>
+        </is>
+      </c>
+      <c r="DH2" s="7" t="inlineStr">
+        <is>
+          <t>Пн</t>
+        </is>
+      </c>
+      <c r="DI2" s="7" t="inlineStr">
+        <is>
+          <t>Вт</t>
+        </is>
+      </c>
+      <c r="DJ2" s="7" t="inlineStr">
+        <is>
+          <t>Ср</t>
+        </is>
+      </c>
+      <c r="DK2" s="7" t="inlineStr">
+        <is>
+          <t>Чт</t>
+        </is>
+      </c>
+      <c r="DL2" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="DM2" s="7" t="inlineStr">
+        <is>
+          <t>Сб</t>
+        </is>
+      </c>
+      <c r="DN2" s="7" t="inlineStr">
+        <is>
+          <t>Вс</t>
+        </is>
+      </c>
+      <c r="DO2" s="7" t="inlineStr">
+        <is>
+          <t>Пн</t>
+        </is>
+      </c>
+      <c r="DP2" s="7" t="inlineStr">
+        <is>
+          <t>Вт</t>
+        </is>
+      </c>
+      <c r="DQ2" s="7" t="inlineStr">
+        <is>
+          <t>Ср</t>
+        </is>
+      </c>
+      <c r="DR2" s="7" t="inlineStr">
+        <is>
+          <t>Чт</t>
+        </is>
+      </c>
+      <c r="DS2" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="DT2" s="7" t="inlineStr">
+        <is>
+          <t>Сб</t>
+        </is>
+      </c>
+      <c r="DU2" s="7" t="inlineStr">
+        <is>
+          <t>Вс</t>
+        </is>
+      </c>
+      <c r="DV2" s="7" t="inlineStr">
+        <is>
+          <t>Пн</t>
+        </is>
+      </c>
+      <c r="DW2" s="7" t="inlineStr">
+        <is>
+          <t>Вт</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Земляные работы и основание</t>
+          <t>Подготовительные работы</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>15.03.2026</t>
+          <t>01.03.2026</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>04.04.2026</t>
+          <t>14.03.2026</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>██</t>
+          <t>■</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>██</t>
+          <t>■</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>██</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr"/>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr"/>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
       <c r="V3" s="3" t="inlineStr"/>
+      <c r="W3" s="3" t="inlineStr"/>
+      <c r="X3" s="3" t="inlineStr"/>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="8" t="inlineStr"/>
+      <c r="AA3" s="8" t="inlineStr"/>
+      <c r="AB3" s="3" t="inlineStr"/>
+      <c r="AC3" s="3" t="inlineStr"/>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr"/>
+      <c r="AF3" s="3" t="inlineStr"/>
+      <c r="AG3" s="8" t="inlineStr"/>
+      <c r="AH3" s="8" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr"/>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr"/>
+      <c r="AM3" s="3" t="inlineStr"/>
+      <c r="AN3" s="8" t="inlineStr"/>
+      <c r="AO3" s="8" t="inlineStr"/>
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr"/>
+      <c r="AS3" s="3" t="inlineStr"/>
+      <c r="AT3" s="3" t="inlineStr"/>
+      <c r="AU3" s="8" t="inlineStr"/>
+      <c r="AV3" s="8" t="inlineStr"/>
+      <c r="AW3" s="3" t="inlineStr"/>
+      <c r="AX3" s="3" t="inlineStr"/>
+      <c r="AY3" s="3" t="inlineStr"/>
+      <c r="AZ3" s="3" t="inlineStr"/>
+      <c r="BA3" s="3" t="inlineStr"/>
+      <c r="BB3" s="8" t="inlineStr"/>
+      <c r="BC3" s="8" t="inlineStr"/>
+      <c r="BD3" s="3" t="inlineStr"/>
+      <c r="BE3" s="3" t="inlineStr"/>
+      <c r="BF3" s="3" t="inlineStr"/>
+      <c r="BG3" s="3" t="inlineStr"/>
+      <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="8" t="inlineStr"/>
+      <c r="BJ3" s="8" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr"/>
+      <c r="BL3" s="3" t="inlineStr"/>
+      <c r="BM3" s="3" t="inlineStr"/>
+      <c r="BN3" s="3" t="inlineStr"/>
+      <c r="BO3" s="3" t="inlineStr"/>
+      <c r="BP3" s="8" t="inlineStr"/>
+      <c r="BQ3" s="8" t="inlineStr"/>
+      <c r="BR3" s="3" t="inlineStr"/>
+      <c r="BS3" s="3" t="inlineStr"/>
+      <c r="BT3" s="3" t="inlineStr"/>
+      <c r="BU3" s="3" t="inlineStr"/>
+      <c r="BV3" s="3" t="inlineStr"/>
+      <c r="BW3" s="8" t="inlineStr"/>
+      <c r="BX3" s="8" t="inlineStr"/>
+      <c r="BY3" s="3" t="inlineStr"/>
+      <c r="BZ3" s="3" t="inlineStr"/>
+      <c r="CA3" s="3" t="inlineStr"/>
+      <c r="CB3" s="3" t="inlineStr"/>
+      <c r="CC3" s="3" t="inlineStr"/>
+      <c r="CD3" s="8" t="inlineStr"/>
+      <c r="CE3" s="8" t="inlineStr"/>
+      <c r="CF3" s="3" t="inlineStr"/>
+      <c r="CG3" s="3" t="inlineStr"/>
+      <c r="CH3" s="3" t="inlineStr"/>
+      <c r="CI3" s="3" t="inlineStr"/>
+      <c r="CJ3" s="3" t="inlineStr"/>
+      <c r="CK3" s="8" t="inlineStr"/>
+      <c r="CL3" s="8" t="inlineStr"/>
+      <c r="CM3" s="3" t="inlineStr"/>
+      <c r="CN3" s="3" t="inlineStr"/>
+      <c r="CO3" s="3" t="inlineStr"/>
+      <c r="CP3" s="3" t="inlineStr"/>
+      <c r="CQ3" s="3" t="inlineStr"/>
+      <c r="CR3" s="8" t="inlineStr"/>
+      <c r="CS3" s="8" t="inlineStr"/>
+      <c r="CT3" s="3" t="inlineStr"/>
+      <c r="CU3" s="3" t="inlineStr"/>
+      <c r="CV3" s="3" t="inlineStr"/>
+      <c r="CW3" s="3" t="inlineStr"/>
+      <c r="CX3" s="3" t="inlineStr"/>
+      <c r="CY3" s="8" t="inlineStr"/>
+      <c r="CZ3" s="8" t="inlineStr"/>
+      <c r="DA3" s="3" t="inlineStr"/>
+      <c r="DB3" s="3" t="inlineStr"/>
+      <c r="DC3" s="3" t="inlineStr"/>
+      <c r="DD3" s="3" t="inlineStr"/>
+      <c r="DE3" s="3" t="inlineStr"/>
+      <c r="DF3" s="8" t="inlineStr"/>
+      <c r="DG3" s="8" t="inlineStr"/>
+      <c r="DH3" s="3" t="inlineStr"/>
+      <c r="DI3" s="3" t="inlineStr"/>
+      <c r="DJ3" s="3" t="inlineStr"/>
+      <c r="DK3" s="3" t="inlineStr"/>
+      <c r="DL3" s="3" t="inlineStr"/>
+      <c r="DM3" s="8" t="inlineStr"/>
+      <c r="DN3" s="8" t="inlineStr"/>
+      <c r="DO3" s="3" t="inlineStr"/>
+      <c r="DP3" s="3" t="inlineStr"/>
+      <c r="DQ3" s="3" t="inlineStr"/>
+      <c r="DR3" s="3" t="inlineStr"/>
+      <c r="DS3" s="3" t="inlineStr"/>
+      <c r="DT3" s="8" t="inlineStr"/>
+      <c r="DU3" s="8" t="inlineStr"/>
+      <c r="DV3" s="3" t="inlineStr"/>
+      <c r="DW3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Устройство фундамента</t>
+          <t>Земляные работы и основание</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>05.04.2026</t>
+          <t>15.03.2026</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>25.04.2026</t>
+          <t>04.04.2026</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="F4" s="3" t="inlineStr"/>
+      <c r="F4" s="8" t="inlineStr"/>
       <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="inlineStr"/>
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>██</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>██</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>██</t>
-        </is>
-      </c>
+      <c r="K4" s="3" t="inlineStr"/>
+      <c r="L4" s="8" t="inlineStr"/>
+      <c r="M4" s="8" t="inlineStr"/>
       <c r="N4" s="3" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr"/>
       <c r="P4" s="3" t="inlineStr"/>
       <c r="Q4" s="3" t="inlineStr"/>
       <c r="R4" s="3" t="inlineStr"/>
-      <c r="S4" s="3" t="inlineStr"/>
-      <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="3" t="inlineStr"/>
-      <c r="V4" s="3" t="inlineStr"/>
+      <c r="S4" s="8" t="inlineStr"/>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="X4" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="Z4" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="AA4" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="AB4" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="AC4" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="AD4" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="AE4" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="AF4" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="AG4" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="AH4" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="AI4" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="AJ4" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="AK4" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="AL4" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="AM4" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="AN4" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="AO4" s="8" t="inlineStr"/>
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr"/>
+      <c r="AS4" s="3" t="inlineStr"/>
+      <c r="AT4" s="3" t="inlineStr"/>
+      <c r="AU4" s="8" t="inlineStr"/>
+      <c r="AV4" s="8" t="inlineStr"/>
+      <c r="AW4" s="3" t="inlineStr"/>
+      <c r="AX4" s="3" t="inlineStr"/>
+      <c r="AY4" s="3" t="inlineStr"/>
+      <c r="AZ4" s="3" t="inlineStr"/>
+      <c r="BA4" s="3" t="inlineStr"/>
+      <c r="BB4" s="8" t="inlineStr"/>
+      <c r="BC4" s="8" t="inlineStr"/>
+      <c r="BD4" s="3" t="inlineStr"/>
+      <c r="BE4" s="3" t="inlineStr"/>
+      <c r="BF4" s="3" t="inlineStr"/>
+      <c r="BG4" s="3" t="inlineStr"/>
+      <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="8" t="inlineStr"/>
+      <c r="BJ4" s="8" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr"/>
+      <c r="BL4" s="3" t="inlineStr"/>
+      <c r="BM4" s="3" t="inlineStr"/>
+      <c r="BN4" s="3" t="inlineStr"/>
+      <c r="BO4" s="3" t="inlineStr"/>
+      <c r="BP4" s="8" t="inlineStr"/>
+      <c r="BQ4" s="8" t="inlineStr"/>
+      <c r="BR4" s="3" t="inlineStr"/>
+      <c r="BS4" s="3" t="inlineStr"/>
+      <c r="BT4" s="3" t="inlineStr"/>
+      <c r="BU4" s="3" t="inlineStr"/>
+      <c r="BV4" s="3" t="inlineStr"/>
+      <c r="BW4" s="8" t="inlineStr"/>
+      <c r="BX4" s="8" t="inlineStr"/>
+      <c r="BY4" s="3" t="inlineStr"/>
+      <c r="BZ4" s="3" t="inlineStr"/>
+      <c r="CA4" s="3" t="inlineStr"/>
+      <c r="CB4" s="3" t="inlineStr"/>
+      <c r="CC4" s="3" t="inlineStr"/>
+      <c r="CD4" s="8" t="inlineStr"/>
+      <c r="CE4" s="8" t="inlineStr"/>
+      <c r="CF4" s="3" t="inlineStr"/>
+      <c r="CG4" s="3" t="inlineStr"/>
+      <c r="CH4" s="3" t="inlineStr"/>
+      <c r="CI4" s="3" t="inlineStr"/>
+      <c r="CJ4" s="3" t="inlineStr"/>
+      <c r="CK4" s="8" t="inlineStr"/>
+      <c r="CL4" s="8" t="inlineStr"/>
+      <c r="CM4" s="3" t="inlineStr"/>
+      <c r="CN4" s="3" t="inlineStr"/>
+      <c r="CO4" s="3" t="inlineStr"/>
+      <c r="CP4" s="3" t="inlineStr"/>
+      <c r="CQ4" s="3" t="inlineStr"/>
+      <c r="CR4" s="8" t="inlineStr"/>
+      <c r="CS4" s="8" t="inlineStr"/>
+      <c r="CT4" s="3" t="inlineStr"/>
+      <c r="CU4" s="3" t="inlineStr"/>
+      <c r="CV4" s="3" t="inlineStr"/>
+      <c r="CW4" s="3" t="inlineStr"/>
+      <c r="CX4" s="3" t="inlineStr"/>
+      <c r="CY4" s="8" t="inlineStr"/>
+      <c r="CZ4" s="8" t="inlineStr"/>
+      <c r="DA4" s="3" t="inlineStr"/>
+      <c r="DB4" s="3" t="inlineStr"/>
+      <c r="DC4" s="3" t="inlineStr"/>
+      <c r="DD4" s="3" t="inlineStr"/>
+      <c r="DE4" s="3" t="inlineStr"/>
+      <c r="DF4" s="8" t="inlineStr"/>
+      <c r="DG4" s="8" t="inlineStr"/>
+      <c r="DH4" s="3" t="inlineStr"/>
+      <c r="DI4" s="3" t="inlineStr"/>
+      <c r="DJ4" s="3" t="inlineStr"/>
+      <c r="DK4" s="3" t="inlineStr"/>
+      <c r="DL4" s="3" t="inlineStr"/>
+      <c r="DM4" s="8" t="inlineStr"/>
+      <c r="DN4" s="8" t="inlineStr"/>
+      <c r="DO4" s="3" t="inlineStr"/>
+      <c r="DP4" s="3" t="inlineStr"/>
+      <c r="DQ4" s="3" t="inlineStr"/>
+      <c r="DR4" s="3" t="inlineStr"/>
+      <c r="DS4" s="3" t="inlineStr"/>
+      <c r="DT4" s="8" t="inlineStr"/>
+      <c r="DU4" s="8" t="inlineStr"/>
+      <c r="DV4" s="3" t="inlineStr"/>
+      <c r="DW4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Монтаж каркаса</t>
+          <t>Устройство фундамента</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>26.04.2026</t>
+          <t>05.04.2026</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>25.04.2026</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="F5" s="3" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>██</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>██</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="inlineStr">
-        <is>
-          <t>██</t>
-        </is>
-      </c>
-      <c r="Q5" s="4" t="inlineStr">
-        <is>
-          <t>██</t>
-        </is>
-      </c>
+      <c r="L5" s="8" t="inlineStr"/>
+      <c r="M5" s="8" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
       <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr"/>
+      <c r="S5" s="8" t="inlineStr"/>
+      <c r="T5" s="8" t="inlineStr"/>
       <c r="U5" s="3" t="inlineStr"/>
       <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="inlineStr"/>
+      <c r="Y5" s="3" t="inlineStr"/>
+      <c r="Z5" s="8" t="inlineStr"/>
+      <c r="AA5" s="8" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr"/>
+      <c r="AC5" s="3" t="inlineStr"/>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr"/>
+      <c r="AF5" s="3" t="inlineStr"/>
+      <c r="AG5" s="8" t="inlineStr"/>
+      <c r="AH5" s="8" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr"/>
+      <c r="AM5" s="3" t="inlineStr"/>
+      <c r="AN5" s="8" t="inlineStr"/>
+      <c r="AO5" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="AP5" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="AQ5" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="AR5" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="AS5" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="AT5" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="AU5" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="AV5" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="AW5" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="AX5" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="AY5" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="AZ5" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="BA5" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="BB5" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="BC5" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="BD5" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="BE5" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="BF5" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="BG5" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="BH5" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="BI5" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="BJ5" s="8" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr"/>
+      <c r="BL5" s="3" t="inlineStr"/>
+      <c r="BM5" s="3" t="inlineStr"/>
+      <c r="BN5" s="3" t="inlineStr"/>
+      <c r="BO5" s="3" t="inlineStr"/>
+      <c r="BP5" s="8" t="inlineStr"/>
+      <c r="BQ5" s="8" t="inlineStr"/>
+      <c r="BR5" s="3" t="inlineStr"/>
+      <c r="BS5" s="3" t="inlineStr"/>
+      <c r="BT5" s="3" t="inlineStr"/>
+      <c r="BU5" s="3" t="inlineStr"/>
+      <c r="BV5" s="3" t="inlineStr"/>
+      <c r="BW5" s="8" t="inlineStr"/>
+      <c r="BX5" s="8" t="inlineStr"/>
+      <c r="BY5" s="3" t="inlineStr"/>
+      <c r="BZ5" s="3" t="inlineStr"/>
+      <c r="CA5" s="3" t="inlineStr"/>
+      <c r="CB5" s="3" t="inlineStr"/>
+      <c r="CC5" s="3" t="inlineStr"/>
+      <c r="CD5" s="8" t="inlineStr"/>
+      <c r="CE5" s="8" t="inlineStr"/>
+      <c r="CF5" s="3" t="inlineStr"/>
+      <c r="CG5" s="3" t="inlineStr"/>
+      <c r="CH5" s="3" t="inlineStr"/>
+      <c r="CI5" s="3" t="inlineStr"/>
+      <c r="CJ5" s="3" t="inlineStr"/>
+      <c r="CK5" s="8" t="inlineStr"/>
+      <c r="CL5" s="8" t="inlineStr"/>
+      <c r="CM5" s="3" t="inlineStr"/>
+      <c r="CN5" s="3" t="inlineStr"/>
+      <c r="CO5" s="3" t="inlineStr"/>
+      <c r="CP5" s="3" t="inlineStr"/>
+      <c r="CQ5" s="3" t="inlineStr"/>
+      <c r="CR5" s="8" t="inlineStr"/>
+      <c r="CS5" s="8" t="inlineStr"/>
+      <c r="CT5" s="3" t="inlineStr"/>
+      <c r="CU5" s="3" t="inlineStr"/>
+      <c r="CV5" s="3" t="inlineStr"/>
+      <c r="CW5" s="3" t="inlineStr"/>
+      <c r="CX5" s="3" t="inlineStr"/>
+      <c r="CY5" s="8" t="inlineStr"/>
+      <c r="CZ5" s="8" t="inlineStr"/>
+      <c r="DA5" s="3" t="inlineStr"/>
+      <c r="DB5" s="3" t="inlineStr"/>
+      <c r="DC5" s="3" t="inlineStr"/>
+      <c r="DD5" s="3" t="inlineStr"/>
+      <c r="DE5" s="3" t="inlineStr"/>
+      <c r="DF5" s="8" t="inlineStr"/>
+      <c r="DG5" s="8" t="inlineStr"/>
+      <c r="DH5" s="3" t="inlineStr"/>
+      <c r="DI5" s="3" t="inlineStr"/>
+      <c r="DJ5" s="3" t="inlineStr"/>
+      <c r="DK5" s="3" t="inlineStr"/>
+      <c r="DL5" s="3" t="inlineStr"/>
+      <c r="DM5" s="8" t="inlineStr"/>
+      <c r="DN5" s="8" t="inlineStr"/>
+      <c r="DO5" s="3" t="inlineStr"/>
+      <c r="DP5" s="3" t="inlineStr"/>
+      <c r="DQ5" s="3" t="inlineStr"/>
+      <c r="DR5" s="3" t="inlineStr"/>
+      <c r="DS5" s="3" t="inlineStr"/>
+      <c r="DT5" s="8" t="inlineStr"/>
+      <c r="DU5" s="8" t="inlineStr"/>
+      <c r="DV5" s="3" t="inlineStr"/>
+      <c r="DW5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Кровля и фасад</t>
+          <t>Монтаж каркаса</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>24.05.2026</t>
+          <t>26.04.2026</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>13.06.2026</t>
+          <t>23.05.2026</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr"/>
       <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="3" t="inlineStr"/>
-      <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr"/>
+      <c r="L6" s="8" t="inlineStr"/>
+      <c r="M6" s="8" t="inlineStr"/>
       <c r="N6" s="3" t="inlineStr"/>
       <c r="O6" s="3" t="inlineStr"/>
       <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr">
-        <is>
-          <t>██</t>
-        </is>
-      </c>
-      <c r="S6" s="4" t="inlineStr">
-        <is>
-          <t>██</t>
-        </is>
-      </c>
-      <c r="T6" s="4" t="inlineStr">
-        <is>
-          <t>██</t>
-        </is>
-      </c>
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="8" t="inlineStr"/>
+      <c r="T6" s="8" t="inlineStr"/>
       <c r="U6" s="3" t="inlineStr"/>
       <c r="V6" s="3" t="inlineStr"/>
+      <c r="W6" s="3" t="inlineStr"/>
+      <c r="X6" s="3" t="inlineStr"/>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="8" t="inlineStr"/>
+      <c r="AA6" s="8" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="AC6" s="3" t="inlineStr"/>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr"/>
+      <c r="AF6" s="3" t="inlineStr"/>
+      <c r="AG6" s="8" t="inlineStr"/>
+      <c r="AH6" s="8" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr"/>
+      <c r="AM6" s="3" t="inlineStr"/>
+      <c r="AN6" s="8" t="inlineStr"/>
+      <c r="AO6" s="8" t="inlineStr"/>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr"/>
+      <c r="AS6" s="3" t="inlineStr"/>
+      <c r="AT6" s="3" t="inlineStr"/>
+      <c r="AU6" s="8" t="inlineStr"/>
+      <c r="AV6" s="8" t="inlineStr"/>
+      <c r="AW6" s="3" t="inlineStr"/>
+      <c r="AX6" s="3" t="inlineStr"/>
+      <c r="AY6" s="3" t="inlineStr"/>
+      <c r="AZ6" s="3" t="inlineStr"/>
+      <c r="BA6" s="3" t="inlineStr"/>
+      <c r="BB6" s="8" t="inlineStr"/>
+      <c r="BC6" s="8" t="inlineStr"/>
+      <c r="BD6" s="3" t="inlineStr"/>
+      <c r="BE6" s="3" t="inlineStr"/>
+      <c r="BF6" s="3" t="inlineStr"/>
+      <c r="BG6" s="3" t="inlineStr"/>
+      <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BI6" s="8" t="inlineStr"/>
+      <c r="BJ6" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="BK6" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="BL6" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="BM6" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="BN6" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="BO6" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="BP6" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="BQ6" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="BR6" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="BS6" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="BT6" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="BU6" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="BV6" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="BW6" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="BX6" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="BY6" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="BZ6" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="CA6" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="CB6" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="CC6" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="CD6" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="CE6" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="CF6" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="CG6" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="CH6" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="CI6" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="CJ6" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="CK6" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="CL6" s="8" t="inlineStr"/>
+      <c r="CM6" s="3" t="inlineStr"/>
+      <c r="CN6" s="3" t="inlineStr"/>
+      <c r="CO6" s="3" t="inlineStr"/>
+      <c r="CP6" s="3" t="inlineStr"/>
+      <c r="CQ6" s="3" t="inlineStr"/>
+      <c r="CR6" s="8" t="inlineStr"/>
+      <c r="CS6" s="8" t="inlineStr"/>
+      <c r="CT6" s="3" t="inlineStr"/>
+      <c r="CU6" s="3" t="inlineStr"/>
+      <c r="CV6" s="3" t="inlineStr"/>
+      <c r="CW6" s="3" t="inlineStr"/>
+      <c r="CX6" s="3" t="inlineStr"/>
+      <c r="CY6" s="8" t="inlineStr"/>
+      <c r="CZ6" s="8" t="inlineStr"/>
+      <c r="DA6" s="3" t="inlineStr"/>
+      <c r="DB6" s="3" t="inlineStr"/>
+      <c r="DC6" s="3" t="inlineStr"/>
+      <c r="DD6" s="3" t="inlineStr"/>
+      <c r="DE6" s="3" t="inlineStr"/>
+      <c r="DF6" s="8" t="inlineStr"/>
+      <c r="DG6" s="8" t="inlineStr"/>
+      <c r="DH6" s="3" t="inlineStr"/>
+      <c r="DI6" s="3" t="inlineStr"/>
+      <c r="DJ6" s="3" t="inlineStr"/>
+      <c r="DK6" s="3" t="inlineStr"/>
+      <c r="DL6" s="3" t="inlineStr"/>
+      <c r="DM6" s="8" t="inlineStr"/>
+      <c r="DN6" s="8" t="inlineStr"/>
+      <c r="DO6" s="3" t="inlineStr"/>
+      <c r="DP6" s="3" t="inlineStr"/>
+      <c r="DQ6" s="3" t="inlineStr"/>
+      <c r="DR6" s="3" t="inlineStr"/>
+      <c r="DS6" s="3" t="inlineStr"/>
+      <c r="DT6" s="8" t="inlineStr"/>
+      <c r="DU6" s="8" t="inlineStr"/>
+      <c r="DV6" s="3" t="inlineStr"/>
+      <c r="DW6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Инженерные сети</t>
+          <t>Кровля и фасад</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>14.06.2026</t>
+          <t>24.05.2026</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>27.06.2026</t>
+          <t>13.06.2026</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="3" t="inlineStr"/>
+      <c r="F7" s="8" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr"/>
+      <c r="L7" s="8" t="inlineStr"/>
+      <c r="M7" s="8" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr"/>
       <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="3" t="inlineStr"/>
-      <c r="U7" s="4" t="inlineStr">
-        <is>
-          <t>██</t>
-        </is>
-      </c>
-      <c r="V7" s="4" t="inlineStr">
-        <is>
-          <t>██</t>
-        </is>
-      </c>
+      <c r="S7" s="8" t="inlineStr"/>
+      <c r="T7" s="8" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr"/>
+      <c r="V7" s="3" t="inlineStr"/>
+      <c r="W7" s="3" t="inlineStr"/>
+      <c r="X7" s="3" t="inlineStr"/>
+      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="Z7" s="8" t="inlineStr"/>
+      <c r="AA7" s="8" t="inlineStr"/>
+      <c r="AB7" s="3" t="inlineStr"/>
+      <c r="AC7" s="3" t="inlineStr"/>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr"/>
+      <c r="AF7" s="3" t="inlineStr"/>
+      <c r="AG7" s="8" t="inlineStr"/>
+      <c r="AH7" s="8" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr"/>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr"/>
+      <c r="AM7" s="3" t="inlineStr"/>
+      <c r="AN7" s="8" t="inlineStr"/>
+      <c r="AO7" s="8" t="inlineStr"/>
+      <c r="AP7" s="3" t="inlineStr"/>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr"/>
+      <c r="AS7" s="3" t="inlineStr"/>
+      <c r="AT7" s="3" t="inlineStr"/>
+      <c r="AU7" s="8" t="inlineStr"/>
+      <c r="AV7" s="8" t="inlineStr"/>
+      <c r="AW7" s="3" t="inlineStr"/>
+      <c r="AX7" s="3" t="inlineStr"/>
+      <c r="AY7" s="3" t="inlineStr"/>
+      <c r="AZ7" s="3" t="inlineStr"/>
+      <c r="BA7" s="3" t="inlineStr"/>
+      <c r="BB7" s="8" t="inlineStr"/>
+      <c r="BC7" s="8" t="inlineStr"/>
+      <c r="BD7" s="3" t="inlineStr"/>
+      <c r="BE7" s="3" t="inlineStr"/>
+      <c r="BF7" s="3" t="inlineStr"/>
+      <c r="BG7" s="3" t="inlineStr"/>
+      <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BI7" s="8" t="inlineStr"/>
+      <c r="BJ7" s="8" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr"/>
+      <c r="BL7" s="3" t="inlineStr"/>
+      <c r="BM7" s="3" t="inlineStr"/>
+      <c r="BN7" s="3" t="inlineStr"/>
+      <c r="BO7" s="3" t="inlineStr"/>
+      <c r="BP7" s="8" t="inlineStr"/>
+      <c r="BQ7" s="8" t="inlineStr"/>
+      <c r="BR7" s="3" t="inlineStr"/>
+      <c r="BS7" s="3" t="inlineStr"/>
+      <c r="BT7" s="3" t="inlineStr"/>
+      <c r="BU7" s="3" t="inlineStr"/>
+      <c r="BV7" s="3" t="inlineStr"/>
+      <c r="BW7" s="8" t="inlineStr"/>
+      <c r="BX7" s="8" t="inlineStr"/>
+      <c r="BY7" s="3" t="inlineStr"/>
+      <c r="BZ7" s="3" t="inlineStr"/>
+      <c r="CA7" s="3" t="inlineStr"/>
+      <c r="CB7" s="3" t="inlineStr"/>
+      <c r="CC7" s="3" t="inlineStr"/>
+      <c r="CD7" s="8" t="inlineStr"/>
+      <c r="CE7" s="8" t="inlineStr"/>
+      <c r="CF7" s="3" t="inlineStr"/>
+      <c r="CG7" s="3" t="inlineStr"/>
+      <c r="CH7" s="3" t="inlineStr"/>
+      <c r="CI7" s="3" t="inlineStr"/>
+      <c r="CJ7" s="3" t="inlineStr"/>
+      <c r="CK7" s="8" t="inlineStr"/>
+      <c r="CL7" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="CM7" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="CN7" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="CO7" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="CP7" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="CQ7" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="CR7" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="CS7" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="CT7" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="CU7" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="CV7" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="CW7" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="CX7" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="CY7" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="CZ7" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="DA7" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="DB7" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="DC7" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="DD7" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="DE7" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="DF7" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="DG7" s="8" t="inlineStr"/>
+      <c r="DH7" s="3" t="inlineStr"/>
+      <c r="DI7" s="3" t="inlineStr"/>
+      <c r="DJ7" s="3" t="inlineStr"/>
+      <c r="DK7" s="3" t="inlineStr"/>
+      <c r="DL7" s="3" t="inlineStr"/>
+      <c r="DM7" s="8" t="inlineStr"/>
+      <c r="DN7" s="8" t="inlineStr"/>
+      <c r="DO7" s="3" t="inlineStr"/>
+      <c r="DP7" s="3" t="inlineStr"/>
+      <c r="DQ7" s="3" t="inlineStr"/>
+      <c r="DR7" s="3" t="inlineStr"/>
+      <c r="DS7" s="3" t="inlineStr"/>
+      <c r="DT7" s="8" t="inlineStr"/>
+      <c r="DU7" s="8" t="inlineStr"/>
+      <c r="DV7" s="3" t="inlineStr"/>
+      <c r="DW7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Отделочные работы и сдача</t>
+          <t>Инженерные сети</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>21.06.2026</t>
+          <t>14.06.2026</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>30.06.2026</t>
+          <t>27.06.2026</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="F8" s="3" t="inlineStr"/>
+      <c r="F8" s="8" t="inlineStr"/>
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr"/>
-      <c r="M8" s="3" t="inlineStr"/>
+      <c r="L8" s="8" t="inlineStr"/>
+      <c r="M8" s="8" t="inlineStr"/>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="inlineStr"/>
       <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" s="3" t="inlineStr"/>
       <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="inlineStr"/>
-      <c r="T8" s="3" t="inlineStr"/>
-      <c r="U8" s="4" t="inlineStr">
-        <is>
-          <t>██</t>
-        </is>
-      </c>
-      <c r="V8" s="4" t="inlineStr">
-        <is>
-          <t>██</t>
+      <c r="S8" s="8" t="inlineStr"/>
+      <c r="T8" s="8" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr"/>
+      <c r="V8" s="3" t="inlineStr"/>
+      <c r="W8" s="3" t="inlineStr"/>
+      <c r="X8" s="3" t="inlineStr"/>
+      <c r="Y8" s="3" t="inlineStr"/>
+      <c r="Z8" s="8" t="inlineStr"/>
+      <c r="AA8" s="8" t="inlineStr"/>
+      <c r="AB8" s="3" t="inlineStr"/>
+      <c r="AC8" s="3" t="inlineStr"/>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr"/>
+      <c r="AF8" s="3" t="inlineStr"/>
+      <c r="AG8" s="8" t="inlineStr"/>
+      <c r="AH8" s="8" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr"/>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr"/>
+      <c r="AM8" s="3" t="inlineStr"/>
+      <c r="AN8" s="8" t="inlineStr"/>
+      <c r="AO8" s="8" t="inlineStr"/>
+      <c r="AP8" s="3" t="inlineStr"/>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr"/>
+      <c r="AS8" s="3" t="inlineStr"/>
+      <c r="AT8" s="3" t="inlineStr"/>
+      <c r="AU8" s="8" t="inlineStr"/>
+      <c r="AV8" s="8" t="inlineStr"/>
+      <c r="AW8" s="3" t="inlineStr"/>
+      <c r="AX8" s="3" t="inlineStr"/>
+      <c r="AY8" s="3" t="inlineStr"/>
+      <c r="AZ8" s="3" t="inlineStr"/>
+      <c r="BA8" s="3" t="inlineStr"/>
+      <c r="BB8" s="8" t="inlineStr"/>
+      <c r="BC8" s="8" t="inlineStr"/>
+      <c r="BD8" s="3" t="inlineStr"/>
+      <c r="BE8" s="3" t="inlineStr"/>
+      <c r="BF8" s="3" t="inlineStr"/>
+      <c r="BG8" s="3" t="inlineStr"/>
+      <c r="BH8" s="3" t="inlineStr"/>
+      <c r="BI8" s="8" t="inlineStr"/>
+      <c r="BJ8" s="8" t="inlineStr"/>
+      <c r="BK8" s="3" t="inlineStr"/>
+      <c r="BL8" s="3" t="inlineStr"/>
+      <c r="BM8" s="3" t="inlineStr"/>
+      <c r="BN8" s="3" t="inlineStr"/>
+      <c r="BO8" s="3" t="inlineStr"/>
+      <c r="BP8" s="8" t="inlineStr"/>
+      <c r="BQ8" s="8" t="inlineStr"/>
+      <c r="BR8" s="3" t="inlineStr"/>
+      <c r="BS8" s="3" t="inlineStr"/>
+      <c r="BT8" s="3" t="inlineStr"/>
+      <c r="BU8" s="3" t="inlineStr"/>
+      <c r="BV8" s="3" t="inlineStr"/>
+      <c r="BW8" s="8" t="inlineStr"/>
+      <c r="BX8" s="8" t="inlineStr"/>
+      <c r="BY8" s="3" t="inlineStr"/>
+      <c r="BZ8" s="3" t="inlineStr"/>
+      <c r="CA8" s="3" t="inlineStr"/>
+      <c r="CB8" s="3" t="inlineStr"/>
+      <c r="CC8" s="3" t="inlineStr"/>
+      <c r="CD8" s="8" t="inlineStr"/>
+      <c r="CE8" s="8" t="inlineStr"/>
+      <c r="CF8" s="3" t="inlineStr"/>
+      <c r="CG8" s="3" t="inlineStr"/>
+      <c r="CH8" s="3" t="inlineStr"/>
+      <c r="CI8" s="3" t="inlineStr"/>
+      <c r="CJ8" s="3" t="inlineStr"/>
+      <c r="CK8" s="8" t="inlineStr"/>
+      <c r="CL8" s="8" t="inlineStr"/>
+      <c r="CM8" s="3" t="inlineStr"/>
+      <c r="CN8" s="3" t="inlineStr"/>
+      <c r="CO8" s="3" t="inlineStr"/>
+      <c r="CP8" s="3" t="inlineStr"/>
+      <c r="CQ8" s="3" t="inlineStr"/>
+      <c r="CR8" s="8" t="inlineStr"/>
+      <c r="CS8" s="8" t="inlineStr"/>
+      <c r="CT8" s="3" t="inlineStr"/>
+      <c r="CU8" s="3" t="inlineStr"/>
+      <c r="CV8" s="3" t="inlineStr"/>
+      <c r="CW8" s="3" t="inlineStr"/>
+      <c r="CX8" s="3" t="inlineStr"/>
+      <c r="CY8" s="8" t="inlineStr"/>
+      <c r="CZ8" s="8" t="inlineStr"/>
+      <c r="DA8" s="3" t="inlineStr"/>
+      <c r="DB8" s="3" t="inlineStr"/>
+      <c r="DC8" s="3" t="inlineStr"/>
+      <c r="DD8" s="3" t="inlineStr"/>
+      <c r="DE8" s="3" t="inlineStr"/>
+      <c r="DF8" s="8" t="inlineStr"/>
+      <c r="DG8" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="DH8" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="DI8" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="DJ8" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="DK8" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="DL8" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="DM8" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="DN8" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="DO8" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="DP8" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="DQ8" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="DR8" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="DS8" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="DT8" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="DU8" s="8" t="inlineStr"/>
+      <c r="DV8" s="3" t="inlineStr"/>
+      <c r="DW8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Отделочные работы и сдача</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>21.06.2026</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>30.06.2026</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" s="8" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="8" t="inlineStr"/>
+      <c r="M9" s="8" t="inlineStr"/>
+      <c r="N9" s="3" t="inlineStr"/>
+      <c r="O9" s="3" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr"/>
+      <c r="S9" s="8" t="inlineStr"/>
+      <c r="T9" s="8" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr"/>
+      <c r="V9" s="3" t="inlineStr"/>
+      <c r="W9" s="3" t="inlineStr"/>
+      <c r="X9" s="3" t="inlineStr"/>
+      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Z9" s="8" t="inlineStr"/>
+      <c r="AA9" s="8" t="inlineStr"/>
+      <c r="AB9" s="3" t="inlineStr"/>
+      <c r="AC9" s="3" t="inlineStr"/>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr"/>
+      <c r="AF9" s="3" t="inlineStr"/>
+      <c r="AG9" s="8" t="inlineStr"/>
+      <c r="AH9" s="8" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr"/>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr"/>
+      <c r="AM9" s="3" t="inlineStr"/>
+      <c r="AN9" s="8" t="inlineStr"/>
+      <c r="AO9" s="8" t="inlineStr"/>
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr"/>
+      <c r="AS9" s="3" t="inlineStr"/>
+      <c r="AT9" s="3" t="inlineStr"/>
+      <c r="AU9" s="8" t="inlineStr"/>
+      <c r="AV9" s="8" t="inlineStr"/>
+      <c r="AW9" s="3" t="inlineStr"/>
+      <c r="AX9" s="3" t="inlineStr"/>
+      <c r="AY9" s="3" t="inlineStr"/>
+      <c r="AZ9" s="3" t="inlineStr"/>
+      <c r="BA9" s="3" t="inlineStr"/>
+      <c r="BB9" s="8" t="inlineStr"/>
+      <c r="BC9" s="8" t="inlineStr"/>
+      <c r="BD9" s="3" t="inlineStr"/>
+      <c r="BE9" s="3" t="inlineStr"/>
+      <c r="BF9" s="3" t="inlineStr"/>
+      <c r="BG9" s="3" t="inlineStr"/>
+      <c r="BH9" s="3" t="inlineStr"/>
+      <c r="BI9" s="8" t="inlineStr"/>
+      <c r="BJ9" s="8" t="inlineStr"/>
+      <c r="BK9" s="3" t="inlineStr"/>
+      <c r="BL9" s="3" t="inlineStr"/>
+      <c r="BM9" s="3" t="inlineStr"/>
+      <c r="BN9" s="3" t="inlineStr"/>
+      <c r="BO9" s="3" t="inlineStr"/>
+      <c r="BP9" s="8" t="inlineStr"/>
+      <c r="BQ9" s="8" t="inlineStr"/>
+      <c r="BR9" s="3" t="inlineStr"/>
+      <c r="BS9" s="3" t="inlineStr"/>
+      <c r="BT9" s="3" t="inlineStr"/>
+      <c r="BU9" s="3" t="inlineStr"/>
+      <c r="BV9" s="3" t="inlineStr"/>
+      <c r="BW9" s="8" t="inlineStr"/>
+      <c r="BX9" s="8" t="inlineStr"/>
+      <c r="BY9" s="3" t="inlineStr"/>
+      <c r="BZ9" s="3" t="inlineStr"/>
+      <c r="CA9" s="3" t="inlineStr"/>
+      <c r="CB9" s="3" t="inlineStr"/>
+      <c r="CC9" s="3" t="inlineStr"/>
+      <c r="CD9" s="8" t="inlineStr"/>
+      <c r="CE9" s="8" t="inlineStr"/>
+      <c r="CF9" s="3" t="inlineStr"/>
+      <c r="CG9" s="3" t="inlineStr"/>
+      <c r="CH9" s="3" t="inlineStr"/>
+      <c r="CI9" s="3" t="inlineStr"/>
+      <c r="CJ9" s="3" t="inlineStr"/>
+      <c r="CK9" s="8" t="inlineStr"/>
+      <c r="CL9" s="8" t="inlineStr"/>
+      <c r="CM9" s="3" t="inlineStr"/>
+      <c r="CN9" s="3" t="inlineStr"/>
+      <c r="CO9" s="3" t="inlineStr"/>
+      <c r="CP9" s="3" t="inlineStr"/>
+      <c r="CQ9" s="3" t="inlineStr"/>
+      <c r="CR9" s="8" t="inlineStr"/>
+      <c r="CS9" s="8" t="inlineStr"/>
+      <c r="CT9" s="3" t="inlineStr"/>
+      <c r="CU9" s="3" t="inlineStr"/>
+      <c r="CV9" s="3" t="inlineStr"/>
+      <c r="CW9" s="3" t="inlineStr"/>
+      <c r="CX9" s="3" t="inlineStr"/>
+      <c r="CY9" s="8" t="inlineStr"/>
+      <c r="CZ9" s="8" t="inlineStr"/>
+      <c r="DA9" s="3" t="inlineStr"/>
+      <c r="DB9" s="3" t="inlineStr"/>
+      <c r="DC9" s="3" t="inlineStr"/>
+      <c r="DD9" s="3" t="inlineStr"/>
+      <c r="DE9" s="3" t="inlineStr"/>
+      <c r="DF9" s="8" t="inlineStr"/>
+      <c r="DG9" s="8" t="inlineStr"/>
+      <c r="DH9" s="3" t="inlineStr"/>
+      <c r="DI9" s="3" t="inlineStr"/>
+      <c r="DJ9" s="3" t="inlineStr"/>
+      <c r="DK9" s="3" t="inlineStr"/>
+      <c r="DL9" s="3" t="inlineStr"/>
+      <c r="DM9" s="8" t="inlineStr"/>
+      <c r="DN9" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="DO9" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="DP9" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="DQ9" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="DR9" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="DS9" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="DT9" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="DU9" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="DV9" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="DW9" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
         </is>
       </c>
     </row>

--- a/linear_schedule.xlsx
+++ b/linear_schedule.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,8 +34,14 @@
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
+    <font>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -66,6 +72,12 @@
         <bgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E06666"/>
+        <bgColor rgb="00E06666"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -93,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -119,6 +131,16 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -484,13 +506,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DW9"/>
+  <dimension ref="A1:DW16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="4.2" customWidth="1" min="6" max="6"/>
     <col width="4.2" customWidth="1" min="7" max="7"/>
@@ -634,7 +656,7 @@
       </c>
       <c r="D1" s="6" t="inlineStr">
         <is>
-          <t>Длит., дн</t>
+          <t>Длит., раб.дн</t>
         </is>
       </c>
       <c r="E1" s="6" t="inlineStr">
@@ -677,7 +699,7 @@
           <t>07.03</t>
         </is>
       </c>
-      <c r="M1" s="6" t="inlineStr">
+      <c r="M1" s="9" t="inlineStr">
         <is>
           <t>08.03</t>
         </is>
@@ -947,7 +969,7 @@
           <t>30.04</t>
         </is>
       </c>
-      <c r="BO1" s="6" t="inlineStr">
+      <c r="BO1" s="9" t="inlineStr">
         <is>
           <t>01.05</t>
         </is>
@@ -987,7 +1009,7 @@
           <t>08.05</t>
         </is>
       </c>
-      <c r="BW1" s="6" t="inlineStr">
+      <c r="BW1" s="9" t="inlineStr">
         <is>
           <t>09.05</t>
         </is>
@@ -1157,7 +1179,7 @@
           <t>11.06</t>
         </is>
       </c>
-      <c r="DE1" s="6" t="inlineStr">
+      <c r="DE1" s="9" t="inlineStr">
         <is>
           <t>12.06</t>
         </is>
@@ -1294,7 +1316,7 @@
           <t>Сб</t>
         </is>
       </c>
-      <c r="M2" s="7" t="inlineStr">
+      <c r="M2" s="9" t="inlineStr">
         <is>
           <t>Вс</t>
         </is>
@@ -1564,7 +1586,7 @@
           <t>Чт</t>
         </is>
       </c>
-      <c r="BO2" s="7" t="inlineStr">
+      <c r="BO2" s="9" t="inlineStr">
         <is>
           <t>Пт</t>
         </is>
@@ -1604,7 +1626,7 @@
           <t>Пт</t>
         </is>
       </c>
-      <c r="BW2" s="7" t="inlineStr">
+      <c r="BW2" s="9" t="inlineStr">
         <is>
           <t>Сб</t>
         </is>
@@ -1774,7 +1796,7 @@
           <t>Чт</t>
         </is>
       </c>
-      <c r="DE2" s="7" t="inlineStr">
+      <c r="DE2" s="9" t="inlineStr">
         <is>
           <t>Пт</t>
         </is>
@@ -1878,25 +1900,21 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>01.03.2026</t>
+          <t>02.03.2026</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>14.03.2026</t>
+          <t>13.03.2026</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
+      <c r="F3" s="8" t="inlineStr"/>
       <c r="G3" s="4" t="inlineStr">
         <is>
           <t>■</t>
@@ -1922,16 +1940,8 @@
           <t>■</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
+      <c r="L3" s="8" t="inlineStr"/>
+      <c r="M3" s="10" t="inlineStr"/>
       <c r="N3" s="4" t="inlineStr">
         <is>
           <t>■</t>
@@ -1957,11 +1967,7 @@
           <t>■</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
+      <c r="S3" s="8" t="inlineStr"/>
       <c r="T3" s="8" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
       <c r="V3" s="3" t="inlineStr"/>
@@ -2009,7 +2015,7 @@
       <c r="BL3" s="3" t="inlineStr"/>
       <c r="BM3" s="3" t="inlineStr"/>
       <c r="BN3" s="3" t="inlineStr"/>
-      <c r="BO3" s="3" t="inlineStr"/>
+      <c r="BO3" s="10" t="inlineStr"/>
       <c r="BP3" s="8" t="inlineStr"/>
       <c r="BQ3" s="8" t="inlineStr"/>
       <c r="BR3" s="3" t="inlineStr"/>
@@ -2017,7 +2023,7 @@
       <c r="BT3" s="3" t="inlineStr"/>
       <c r="BU3" s="3" t="inlineStr"/>
       <c r="BV3" s="3" t="inlineStr"/>
-      <c r="BW3" s="8" t="inlineStr"/>
+      <c r="BW3" s="10" t="inlineStr"/>
       <c r="BX3" s="8" t="inlineStr"/>
       <c r="BY3" s="3" t="inlineStr"/>
       <c r="BZ3" s="3" t="inlineStr"/>
@@ -2051,7 +2057,7 @@
       <c r="DB3" s="3" t="inlineStr"/>
       <c r="DC3" s="3" t="inlineStr"/>
       <c r="DD3" s="3" t="inlineStr"/>
-      <c r="DE3" s="3" t="inlineStr"/>
+      <c r="DE3" s="10" t="inlineStr"/>
       <c r="DF3" s="8" t="inlineStr"/>
       <c r="DG3" s="8" t="inlineStr"/>
       <c r="DH3" s="3" t="inlineStr"/>
@@ -2079,16 +2085,16 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>15.03.2026</t>
+          <t>16.03.2026</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>04.04.2026</t>
+          <t>03.04.2026</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>5</v>
@@ -2100,18 +2106,14 @@
       <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="3" t="inlineStr"/>
       <c r="L4" s="8" t="inlineStr"/>
-      <c r="M4" s="8" t="inlineStr"/>
+      <c r="M4" s="10" t="inlineStr"/>
       <c r="N4" s="3" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr"/>
       <c r="P4" s="3" t="inlineStr"/>
       <c r="Q4" s="3" t="inlineStr"/>
       <c r="R4" s="3" t="inlineStr"/>
       <c r="S4" s="8" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
+      <c r="T4" s="8" t="inlineStr"/>
       <c r="U4" s="4" t="inlineStr">
         <is>
           <t>■</t>
@@ -2137,16 +2139,8 @@
           <t>■</t>
         </is>
       </c>
-      <c r="Z4" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="AA4" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
+      <c r="Z4" s="8" t="inlineStr"/>
+      <c r="AA4" s="8" t="inlineStr"/>
       <c r="AB4" s="4" t="inlineStr">
         <is>
           <t>■</t>
@@ -2172,16 +2166,8 @@
           <t>■</t>
         </is>
       </c>
-      <c r="AG4" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="AH4" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
+      <c r="AG4" s="8" t="inlineStr"/>
+      <c r="AH4" s="8" t="inlineStr"/>
       <c r="AI4" s="4" t="inlineStr">
         <is>
           <t>■</t>
@@ -2207,11 +2193,7 @@
           <t>■</t>
         </is>
       </c>
-      <c r="AN4" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
+      <c r="AN4" s="8" t="inlineStr"/>
       <c r="AO4" s="8" t="inlineStr"/>
       <c r="AP4" s="3" t="inlineStr"/>
       <c r="AQ4" s="3" t="inlineStr"/>
@@ -2238,7 +2220,7 @@
       <c r="BL4" s="3" t="inlineStr"/>
       <c r="BM4" s="3" t="inlineStr"/>
       <c r="BN4" s="3" t="inlineStr"/>
-      <c r="BO4" s="3" t="inlineStr"/>
+      <c r="BO4" s="10" t="inlineStr"/>
       <c r="BP4" s="8" t="inlineStr"/>
       <c r="BQ4" s="8" t="inlineStr"/>
       <c r="BR4" s="3" t="inlineStr"/>
@@ -2246,7 +2228,7 @@
       <c r="BT4" s="3" t="inlineStr"/>
       <c r="BU4" s="3" t="inlineStr"/>
       <c r="BV4" s="3" t="inlineStr"/>
-      <c r="BW4" s="8" t="inlineStr"/>
+      <c r="BW4" s="10" t="inlineStr"/>
       <c r="BX4" s="8" t="inlineStr"/>
       <c r="BY4" s="3" t="inlineStr"/>
       <c r="BZ4" s="3" t="inlineStr"/>
@@ -2280,7 +2262,7 @@
       <c r="DB4" s="3" t="inlineStr"/>
       <c r="DC4" s="3" t="inlineStr"/>
       <c r="DD4" s="3" t="inlineStr"/>
-      <c r="DE4" s="3" t="inlineStr"/>
+      <c r="DE4" s="10" t="inlineStr"/>
       <c r="DF4" s="8" t="inlineStr"/>
       <c r="DG4" s="8" t="inlineStr"/>
       <c r="DH4" s="3" t="inlineStr"/>
@@ -2308,16 +2290,16 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>05.04.2026</t>
+          <t>06.04.2026</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>25.04.2026</t>
+          <t>24.04.2026</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>5</v>
@@ -2329,7 +2311,7 @@
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="8" t="inlineStr"/>
-      <c r="M5" s="8" t="inlineStr"/>
+      <c r="M5" s="10" t="inlineStr"/>
       <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
@@ -2357,11 +2339,7 @@
       <c r="AL5" s="3" t="inlineStr"/>
       <c r="AM5" s="3" t="inlineStr"/>
       <c r="AN5" s="8" t="inlineStr"/>
-      <c r="AO5" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
+      <c r="AO5" s="8" t="inlineStr"/>
       <c r="AP5" s="4" t="inlineStr">
         <is>
           <t>■</t>
@@ -2387,16 +2365,8 @@
           <t>■</t>
         </is>
       </c>
-      <c r="AU5" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="AV5" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
+      <c r="AU5" s="8" t="inlineStr"/>
+      <c r="AV5" s="8" t="inlineStr"/>
       <c r="AW5" s="4" t="inlineStr">
         <is>
           <t>■</t>
@@ -2422,16 +2392,8 @@
           <t>■</t>
         </is>
       </c>
-      <c r="BB5" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="BC5" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
+      <c r="BB5" s="8" t="inlineStr"/>
+      <c r="BC5" s="8" t="inlineStr"/>
       <c r="BD5" s="4" t="inlineStr">
         <is>
           <t>■</t>
@@ -2457,17 +2419,13 @@
           <t>■</t>
         </is>
       </c>
-      <c r="BI5" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
+      <c r="BI5" s="8" t="inlineStr"/>
       <c r="BJ5" s="8" t="inlineStr"/>
       <c r="BK5" s="3" t="inlineStr"/>
       <c r="BL5" s="3" t="inlineStr"/>
       <c r="BM5" s="3" t="inlineStr"/>
       <c r="BN5" s="3" t="inlineStr"/>
-      <c r="BO5" s="3" t="inlineStr"/>
+      <c r="BO5" s="10" t="inlineStr"/>
       <c r="BP5" s="8" t="inlineStr"/>
       <c r="BQ5" s="8" t="inlineStr"/>
       <c r="BR5" s="3" t="inlineStr"/>
@@ -2475,7 +2433,7 @@
       <c r="BT5" s="3" t="inlineStr"/>
       <c r="BU5" s="3" t="inlineStr"/>
       <c r="BV5" s="3" t="inlineStr"/>
-      <c r="BW5" s="8" t="inlineStr"/>
+      <c r="BW5" s="10" t="inlineStr"/>
       <c r="BX5" s="8" t="inlineStr"/>
       <c r="BY5" s="3" t="inlineStr"/>
       <c r="BZ5" s="3" t="inlineStr"/>
@@ -2509,7 +2467,7 @@
       <c r="DB5" s="3" t="inlineStr"/>
       <c r="DC5" s="3" t="inlineStr"/>
       <c r="DD5" s="3" t="inlineStr"/>
-      <c r="DE5" s="3" t="inlineStr"/>
+      <c r="DE5" s="10" t="inlineStr"/>
       <c r="DF5" s="8" t="inlineStr"/>
       <c r="DG5" s="8" t="inlineStr"/>
       <c r="DH5" s="3" t="inlineStr"/>
@@ -2537,16 +2495,16 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>26.04.2026</t>
+          <t>27.04.2026</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>22.05.2026</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>5</v>
@@ -2558,7 +2516,7 @@
       <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="3" t="inlineStr"/>
       <c r="L6" s="8" t="inlineStr"/>
-      <c r="M6" s="8" t="inlineStr"/>
+      <c r="M6" s="10" t="inlineStr"/>
       <c r="N6" s="3" t="inlineStr"/>
       <c r="O6" s="3" t="inlineStr"/>
       <c r="P6" s="3" t="inlineStr"/>
@@ -2607,11 +2565,7 @@
       <c r="BG6" s="3" t="inlineStr"/>
       <c r="BH6" s="3" t="inlineStr"/>
       <c r="BI6" s="8" t="inlineStr"/>
-      <c r="BJ6" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
+      <c r="BJ6" s="8" t="inlineStr"/>
       <c r="BK6" s="4" t="inlineStr">
         <is>
           <t>■</t>
@@ -2632,21 +2586,9 @@
           <t>■</t>
         </is>
       </c>
-      <c r="BO6" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="BP6" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="BQ6" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
+      <c r="BO6" s="10" t="inlineStr"/>
+      <c r="BP6" s="8" t="inlineStr"/>
+      <c r="BQ6" s="8" t="inlineStr"/>
       <c r="BR6" s="4" t="inlineStr">
         <is>
           <t>■</t>
@@ -2672,16 +2614,8 @@
           <t>■</t>
         </is>
       </c>
-      <c r="BW6" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="BX6" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
+      <c r="BW6" s="10" t="inlineStr"/>
+      <c r="BX6" s="8" t="inlineStr"/>
       <c r="BY6" s="4" t="inlineStr">
         <is>
           <t>■</t>
@@ -2707,16 +2641,8 @@
           <t>■</t>
         </is>
       </c>
-      <c r="CD6" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="CE6" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
+      <c r="CD6" s="8" t="inlineStr"/>
+      <c r="CE6" s="8" t="inlineStr"/>
       <c r="CF6" s="4" t="inlineStr">
         <is>
           <t>■</t>
@@ -2742,11 +2668,7 @@
           <t>■</t>
         </is>
       </c>
-      <c r="CK6" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
+      <c r="CK6" s="8" t="inlineStr"/>
       <c r="CL6" s="8" t="inlineStr"/>
       <c r="CM6" s="3" t="inlineStr"/>
       <c r="CN6" s="3" t="inlineStr"/>
@@ -2766,7 +2688,7 @@
       <c r="DB6" s="3" t="inlineStr"/>
       <c r="DC6" s="3" t="inlineStr"/>
       <c r="DD6" s="3" t="inlineStr"/>
-      <c r="DE6" s="3" t="inlineStr"/>
+      <c r="DE6" s="10" t="inlineStr"/>
       <c r="DF6" s="8" t="inlineStr"/>
       <c r="DG6" s="8" t="inlineStr"/>
       <c r="DH6" s="3" t="inlineStr"/>
@@ -2794,16 +2716,16 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>24.05.2026</t>
+          <t>25.05.2026</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>13.06.2026</t>
+          <t>16.06.2026</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>5</v>
@@ -2815,7 +2737,7 @@
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="8" t="inlineStr"/>
-      <c r="M7" s="8" t="inlineStr"/>
+      <c r="M7" s="10" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
@@ -2869,7 +2791,7 @@
       <c r="BL7" s="3" t="inlineStr"/>
       <c r="BM7" s="3" t="inlineStr"/>
       <c r="BN7" s="3" t="inlineStr"/>
-      <c r="BO7" s="3" t="inlineStr"/>
+      <c r="BO7" s="10" t="inlineStr"/>
       <c r="BP7" s="8" t="inlineStr"/>
       <c r="BQ7" s="8" t="inlineStr"/>
       <c r="BR7" s="3" t="inlineStr"/>
@@ -2877,7 +2799,7 @@
       <c r="BT7" s="3" t="inlineStr"/>
       <c r="BU7" s="3" t="inlineStr"/>
       <c r="BV7" s="3" t="inlineStr"/>
-      <c r="BW7" s="8" t="inlineStr"/>
+      <c r="BW7" s="10" t="inlineStr"/>
       <c r="BX7" s="8" t="inlineStr"/>
       <c r="BY7" s="3" t="inlineStr"/>
       <c r="BZ7" s="3" t="inlineStr"/>
@@ -2892,11 +2814,7 @@
       <c r="CI7" s="3" t="inlineStr"/>
       <c r="CJ7" s="3" t="inlineStr"/>
       <c r="CK7" s="8" t="inlineStr"/>
-      <c r="CL7" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
+      <c r="CL7" s="8" t="inlineStr"/>
       <c r="CM7" s="4" t="inlineStr">
         <is>
           <t>■</t>
@@ -2922,16 +2840,8 @@
           <t>■</t>
         </is>
       </c>
-      <c r="CR7" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="CS7" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
+      <c r="CR7" s="8" t="inlineStr"/>
+      <c r="CS7" s="8" t="inlineStr"/>
       <c r="CT7" s="4" t="inlineStr">
         <is>
           <t>■</t>
@@ -2957,16 +2867,8 @@
           <t>■</t>
         </is>
       </c>
-      <c r="CY7" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="CZ7" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
+      <c r="CY7" s="8" t="inlineStr"/>
+      <c r="CZ7" s="8" t="inlineStr"/>
       <c r="DA7" s="4" t="inlineStr">
         <is>
           <t>■</t>
@@ -2987,19 +2889,19 @@
           <t>■</t>
         </is>
       </c>
-      <c r="DE7" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="DF7" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
+      <c r="DE7" s="10" t="inlineStr"/>
+      <c r="DF7" s="8" t="inlineStr"/>
       <c r="DG7" s="8" t="inlineStr"/>
-      <c r="DH7" s="3" t="inlineStr"/>
-      <c r="DI7" s="3" t="inlineStr"/>
+      <c r="DH7" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
+      <c r="DI7" s="4" t="inlineStr">
+        <is>
+          <t>■</t>
+        </is>
+      </c>
       <c r="DJ7" s="3" t="inlineStr"/>
       <c r="DK7" s="3" t="inlineStr"/>
       <c r="DL7" s="3" t="inlineStr"/>
@@ -3023,16 +2925,16 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>14.06.2026</t>
+          <t>17.06.2026</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>27.06.2026</t>
+          <t>24.06.2026</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>5</v>
@@ -3044,7 +2946,7 @@
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="3" t="inlineStr"/>
       <c r="L8" s="8" t="inlineStr"/>
-      <c r="M8" s="8" t="inlineStr"/>
+      <c r="M8" s="10" t="inlineStr"/>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="inlineStr"/>
       <c r="P8" s="3" t="inlineStr"/>
@@ -3098,7 +3000,7 @@
       <c r="BL8" s="3" t="inlineStr"/>
       <c r="BM8" s="3" t="inlineStr"/>
       <c r="BN8" s="3" t="inlineStr"/>
-      <c r="BO8" s="3" t="inlineStr"/>
+      <c r="BO8" s="10" t="inlineStr"/>
       <c r="BP8" s="8" t="inlineStr"/>
       <c r="BQ8" s="8" t="inlineStr"/>
       <c r="BR8" s="3" t="inlineStr"/>
@@ -3106,7 +3008,7 @@
       <c r="BT8" s="3" t="inlineStr"/>
       <c r="BU8" s="3" t="inlineStr"/>
       <c r="BV8" s="3" t="inlineStr"/>
-      <c r="BW8" s="8" t="inlineStr"/>
+      <c r="BW8" s="10" t="inlineStr"/>
       <c r="BX8" s="8" t="inlineStr"/>
       <c r="BY8" s="3" t="inlineStr"/>
       <c r="BZ8" s="3" t="inlineStr"/>
@@ -3140,23 +3042,11 @@
       <c r="DB8" s="3" t="inlineStr"/>
       <c r="DC8" s="3" t="inlineStr"/>
       <c r="DD8" s="3" t="inlineStr"/>
-      <c r="DE8" s="3" t="inlineStr"/>
+      <c r="DE8" s="10" t="inlineStr"/>
       <c r="DF8" s="8" t="inlineStr"/>
-      <c r="DG8" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="DH8" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="DI8" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
+      <c r="DG8" s="8" t="inlineStr"/>
+      <c r="DH8" s="3" t="inlineStr"/>
+      <c r="DI8" s="3" t="inlineStr"/>
       <c r="DJ8" s="4" t="inlineStr">
         <is>
           <t>■</t>
@@ -3172,16 +3062,8 @@
           <t>■</t>
         </is>
       </c>
-      <c r="DM8" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="DN8" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
+      <c r="DM8" s="8" t="inlineStr"/>
+      <c r="DN8" s="8" t="inlineStr"/>
       <c r="DO8" s="4" t="inlineStr">
         <is>
           <t>■</t>
@@ -3197,21 +3079,9 @@
           <t>■</t>
         </is>
       </c>
-      <c r="DR8" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="DS8" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="DT8" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
+      <c r="DR8" s="3" t="inlineStr"/>
+      <c r="DS8" s="3" t="inlineStr"/>
+      <c r="DT8" s="8" t="inlineStr"/>
       <c r="DU8" s="8" t="inlineStr"/>
       <c r="DV8" s="3" t="inlineStr"/>
       <c r="DW8" s="3" t="inlineStr"/>
@@ -3224,7 +3094,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>21.06.2026</t>
+          <t>25.06.2026</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -3233,7 +3103,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>5</v>
@@ -3245,7 +3115,7 @@
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="8" t="inlineStr"/>
-      <c r="M9" s="8" t="inlineStr"/>
+      <c r="M9" s="10" t="inlineStr"/>
       <c r="N9" s="3" t="inlineStr"/>
       <c r="O9" s="3" t="inlineStr"/>
       <c r="P9" s="3" t="inlineStr"/>
@@ -3299,7 +3169,7 @@
       <c r="BL9" s="3" t="inlineStr"/>
       <c r="BM9" s="3" t="inlineStr"/>
       <c r="BN9" s="3" t="inlineStr"/>
-      <c r="BO9" s="3" t="inlineStr"/>
+      <c r="BO9" s="10" t="inlineStr"/>
       <c r="BP9" s="8" t="inlineStr"/>
       <c r="BQ9" s="8" t="inlineStr"/>
       <c r="BR9" s="3" t="inlineStr"/>
@@ -3307,7 +3177,7 @@
       <c r="BT9" s="3" t="inlineStr"/>
       <c r="BU9" s="3" t="inlineStr"/>
       <c r="BV9" s="3" t="inlineStr"/>
-      <c r="BW9" s="8" t="inlineStr"/>
+      <c r="BW9" s="10" t="inlineStr"/>
       <c r="BX9" s="8" t="inlineStr"/>
       <c r="BY9" s="3" t="inlineStr"/>
       <c r="BZ9" s="3" t="inlineStr"/>
@@ -3341,7 +3211,7 @@
       <c r="DB9" s="3" t="inlineStr"/>
       <c r="DC9" s="3" t="inlineStr"/>
       <c r="DD9" s="3" t="inlineStr"/>
-      <c r="DE9" s="3" t="inlineStr"/>
+      <c r="DE9" s="10" t="inlineStr"/>
       <c r="DF9" s="8" t="inlineStr"/>
       <c r="DG9" s="8" t="inlineStr"/>
       <c r="DH9" s="3" t="inlineStr"/>
@@ -3350,26 +3220,10 @@
       <c r="DK9" s="3" t="inlineStr"/>
       <c r="DL9" s="3" t="inlineStr"/>
       <c r="DM9" s="8" t="inlineStr"/>
-      <c r="DN9" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="DO9" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="DP9" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="DQ9" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
+      <c r="DN9" s="8" t="inlineStr"/>
+      <c r="DO9" s="3" t="inlineStr"/>
+      <c r="DP9" s="3" t="inlineStr"/>
+      <c r="DQ9" s="3" t="inlineStr"/>
       <c r="DR9" s="4" t="inlineStr">
         <is>
           <t>■</t>
@@ -3380,16 +3234,8 @@
           <t>■</t>
         </is>
       </c>
-      <c r="DT9" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="DU9" s="4" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
+      <c r="DT9" s="8" t="inlineStr"/>
+      <c r="DU9" s="8" t="inlineStr"/>
       <c r="DV9" s="4" t="inlineStr">
         <is>
           <t>■</t>
@@ -3398,6 +3244,76 @@
       <c r="DW9" s="4" t="inlineStr">
         <is>
           <t>■</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Легенда цветов</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>   </t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Зеленый</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Рабочий день выполнения этапа</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>   </t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Серый</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Выходной (суббота/воскресенье)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>   </t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Красный</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Праздничный нерабочий день</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>Праздничные дни (без учета переносов):</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>08.03, 01.05, 09.05, 12.06</t>
         </is>
       </c>
     </row>
